--- a/UzTMK/UzTMK_BankBP_Molybdenum_HMP.xlsx
+++ b/UzTMK/UzTMK_BankBP_Molybdenum_HMP.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="552">
   <si>
     <t xml:space="preserve">БИЗНЕС-ПЛАН ИНВЕСТИЦИОННОГО ПРОЕКТА</t>
   </si>
@@ -286,7 +286,7 @@
     <t xml:space="preserve">- Все затраты сверх суммы кредита финансируются за счёт собственных средств заемщика.</t>
   </si>
   <si>
-    <t xml:space="preserve">- Кредит выдаётся единовременно в начале 1-го года; проценты 1-го года капитализируются в стоимость основных средств.</t>
+    <t xml:space="preserve">- Кредит выдаётся единовременно в начале 1-го года; проценты 1-го года отражаются в расходах 1-го года и оплачиваются за счёт собственных средств заемщика.</t>
   </si>
   <si>
     <t xml:space="preserve">- Резерв на непредвиденные расходы - 1% суммы кредита.</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">Приложение 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Линейный метод. Проценты льготного периода капитализированы в стоимость основных средств (МСФО IAS 23).</t>
+    <t xml:space="preserve">Линейный метод.</t>
   </si>
   <si>
     <t xml:space="preserve">ОБЪЕКТЫ АМОРТИЗАЦИИ</t>
@@ -683,12 +683,6 @@
     <t xml:space="preserve">Поддерживающие капвложения (% от первоначальной стоимости ОС)</t>
   </si>
   <si>
-    <t xml:space="preserve">Капитализированные проценты по кредиту за льготный период (1-й год)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Затраты по займам (МСФО IAS 23)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Х</t>
   </si>
   <si>
@@ -1334,7 +1328,7 @@
     <t xml:space="preserve">ФИНАНСОВЫЕ ИЗДЕРЖКИ</t>
   </si>
   <si>
-    <t xml:space="preserve">   Проценты за кредит (1-й год - капитализированы, оплачены за счёт собственных средств)</t>
+    <t xml:space="preserve">   Проценты за кредит (1-й год - за счёт собственных средств заемщика)</t>
   </si>
   <si>
     <t xml:space="preserve">ПОЛНАЯ СТОИМОСТЬ ПРОДАННОЙ ПРОДУКЦИИ</t>
@@ -1487,7 +1481,7 @@
     <t xml:space="preserve">Долг / EBITDA</t>
   </si>
   <si>
-    <t xml:space="preserve">1-й год: проценты за кредит льготного периода оплачиваются за счёт собственных средств и капитализируются в стоимость основных средств (МСФО IAS 23, Приложения 1 и 4); в отчёт о прибылях и убытках не включаются.</t>
+    <t xml:space="preserve">1-й год: проценты за кредит льготного периода отражены в расходах 1-го года и оплачиваются за счёт собственных средств заемщика (включены в стоимость проекта, Приложение 1).</t>
   </si>
   <si>
     <t xml:space="preserve">ПРЕДПОЛОЖЕНИЯ ПО РАБОЧЕМУ КАПИТАЛУ (в экв. долл. США)</t>
@@ -1607,7 +1601,7 @@
     <t xml:space="preserve">Проценты за кредит (B)</t>
   </si>
   <si>
-    <t xml:space="preserve">Прочие финансовые издержки в инвестиционный период (проценты льготного периода)</t>
+    <t xml:space="preserve">Прочие финансовые издержки в инвестиционный период</t>
   </si>
   <si>
     <t xml:space="preserve">Чистые поступления наличности</t>
@@ -2140,10 +2134,6 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2194,6 +2184,10 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -2994,7 +2988,7 @@
       </c>
       <c r="D39" s="14" t="n">
         <f aca="false">ProfLoss!D27</f>
-        <v>731448.935790863</v>
+        <v>731448.935790864</v>
       </c>
       <c r="E39" s="14" t="n">
         <f aca="false">ProfLoss!E27</f>
@@ -3030,31 +3024,31 @@
       </c>
       <c r="D40" s="14" t="n">
         <f aca="false">ProfLoss!D22</f>
-        <v>54544.3369456143</v>
+        <v>-1205425.09752808</v>
       </c>
       <c r="E40" s="14" t="n">
         <f aca="false">ProfLoss!E22</f>
-        <v>6229315.91001298</v>
+        <v>6483292.77090284</v>
       </c>
       <c r="F40" s="14" t="n">
         <f aca="false">ProfLoss!F22</f>
-        <v>11113129.4510666</v>
+        <v>11186292.5473273</v>
       </c>
       <c r="G40" s="14" t="n">
         <f aca="false">ProfLoss!G22</f>
-        <v>15106555.3057021</v>
+        <v>15179718.4019627</v>
       </c>
       <c r="H40" s="14" t="n">
         <f aca="false">ProfLoss!H22</f>
-        <v>15720249.7962481</v>
+        <v>15793412.8925087</v>
       </c>
       <c r="I40" s="14" t="n">
         <f aca="false">ProfLoss!I22</f>
-        <v>16284124.4541199</v>
+        <v>16357287.5503806</v>
       </c>
       <c r="J40" s="14" t="n">
         <f aca="false">ProfLoss!J22</f>
-        <v>16859495.8586853</v>
+        <v>16932658.9549459</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3066,31 +3060,31 @@
       </c>
       <c r="D41" s="14" t="n">
         <f aca="false">CashFlow!D18</f>
-        <v>-12856917.8800911</v>
+        <v>-12847292.4088654</v>
       </c>
       <c r="E41" s="14" t="n">
         <f aca="false">CashFlow!E18</f>
-        <v>16865939.9007855</v>
+        <v>17033842.5307805</v>
       </c>
       <c r="F41" s="14" t="n">
         <f aca="false">CashFlow!F18</f>
-        <v>13020260.6447673</v>
+        <v>13007349.510133</v>
       </c>
       <c r="G41" s="14" t="n">
         <f aca="false">CashFlow!G18</f>
-        <v>17181750.2820009</v>
+        <v>17168839.1473667</v>
       </c>
       <c r="H41" s="14" t="n">
         <f aca="false">CashFlow!H18</f>
-        <v>18926303.9741256</v>
+        <v>18913392.8394914</v>
       </c>
       <c r="I41" s="14" t="n">
         <f aca="false">CashFlow!I18</f>
-        <v>19356302.0598304</v>
+        <v>19343390.9251962</v>
       </c>
       <c r="J41" s="14" t="n">
         <f aca="false">CashFlow!J18</f>
-        <v>19764802.3872907</v>
+        <v>19751891.2526565</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3138,31 +3132,31 @@
       </c>
       <c r="D43" s="14" t="n">
         <f aca="false">CashFlow!D26</f>
-        <v>903741.604225626</v>
+        <v>913367.075451335</v>
       </c>
       <c r="E43" s="14" t="n">
         <f aca="false">CashFlow!E26</f>
-        <v>12098864.6638843</v>
+        <v>12266767.2938792</v>
       </c>
       <c r="F43" s="14" t="n">
         <f aca="false">CashFlow!F26</f>
-        <v>8471859.15313605</v>
+        <v>8458948.01850181</v>
       </c>
       <c r="G43" s="14" t="n">
         <f aca="false">CashFlow!G26</f>
-        <v>12848534.3676069</v>
+        <v>12835623.2329727</v>
       </c>
       <c r="H43" s="14" t="n">
         <f aca="false">CashFlow!H26</f>
-        <v>14808273.6369688</v>
+        <v>14795362.5023346</v>
       </c>
       <c r="I43" s="14" t="n">
         <f aca="false">CashFlow!I26</f>
-        <v>15452327.3299847</v>
+        <v>15439416.1953504</v>
       </c>
       <c r="J43" s="14" t="n">
         <f aca="false">CashFlow!J26</f>
-        <v>16077143.2046083</v>
+        <v>16064232.069974</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3174,31 +3168,31 @@
       </c>
       <c r="D44" s="14" t="n">
         <f aca="false">CashFlow!D27</f>
-        <v>903741.604225626</v>
+        <v>913367.075451335</v>
       </c>
       <c r="E44" s="14" t="n">
         <f aca="false">CashFlow!E27</f>
-        <v>13002606.2681099</v>
+        <v>13180134.3693306</v>
       </c>
       <c r="F44" s="14" t="n">
         <f aca="false">CashFlow!F27</f>
-        <v>21474465.4212459</v>
+        <v>21639082.3878324</v>
       </c>
       <c r="G44" s="14" t="n">
         <f aca="false">CashFlow!G27</f>
-        <v>34322999.7888528</v>
+        <v>34474705.6208051</v>
       </c>
       <c r="H44" s="14" t="n">
         <f aca="false">CashFlow!H27</f>
-        <v>49131273.4258216</v>
+        <v>49270068.1231396</v>
       </c>
       <c r="I44" s="14" t="n">
         <f aca="false">CashFlow!I27</f>
-        <v>64583600.7558063</v>
+        <v>64709484.31849</v>
       </c>
       <c r="J44" s="14" t="n">
         <f aca="false">CashFlow!J27</f>
-        <v>80660743.9604145</v>
+        <v>80773716.3884641</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3214,27 +3208,27 @@
       </c>
       <c r="E45" s="21" t="n">
         <f aca="false">CashFlow!E30</f>
-        <v>3.86195860075513</v>
+        <v>3.90167558159202</v>
       </c>
       <c r="F45" s="21" t="n">
         <f aca="false">CashFlow!F30</f>
-        <v>3.11331368552493</v>
+        <v>3.11009299015867</v>
       </c>
       <c r="G45" s="21" t="n">
         <f aca="false">CashFlow!G30</f>
-        <v>4.38688156350384</v>
+        <v>4.38347818047154</v>
       </c>
       <c r="H45" s="21" t="n">
         <f aca="false">CashFlow!H30</f>
-        <v>5.13820145052185</v>
+        <v>5.13459340832996</v>
       </c>
       <c r="I45" s="21" t="n">
         <f aca="false">CashFlow!I30</f>
-        <v>5.59292429167083</v>
+        <v>5.58908669085975</v>
       </c>
       <c r="J45" s="21" t="n">
         <f aca="false">CashFlow!J30</f>
-        <v>6.1069984291019</v>
+        <v>6.1028971317846</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3293,7 +3287,7 @@
       </c>
       <c r="C49" s="22" t="n">
         <f aca="false">NPV_IRR!D18</f>
-        <v>2921942.35760998</v>
+        <v>3028010.79740899</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3302,7 +3296,7 @@
       </c>
       <c r="C50" s="23" t="n">
         <f aca="false">NPV_IRR!D19</f>
-        <v>0.127593983562719</v>
+        <v>0.128193840540597</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3311,7 +3305,7 @@
       </c>
       <c r="C51" s="24" t="n">
         <f aca="false">NPV_IRR!D20</f>
-        <v>1.04851782462375</v>
+        <v>1.0502862832774</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3320,7 +3314,7 @@
       </c>
       <c r="C52" s="25" t="n">
         <f aca="false">NPV_IRR!D21</f>
-        <v>5.16558483930142</v>
+        <v>5.15831732629757</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3329,7 +3323,7 @@
       </c>
       <c r="C53" s="25" t="n">
         <f aca="false">NPV_IRR!D22</f>
-        <v>6.68104001674324</v>
+        <v>6.66923942844867</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3349,7 +3343,7 @@
       </c>
       <c r="C55" s="23" t="n">
         <f aca="false">BreakPoint!C10</f>
-        <v>0.350149080497285</v>
+        <v>0.34707320245053</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3381,7 +3375,7 @@
       </c>
       <c r="C59" s="27" t="str">
         <f aca="false">IF(MIN(ProfLoss!D22:J22)&gt;0,"Да","Нет")</f>
-        <v>Да</v>
+        <v>Нет</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3674,45 +3668,45 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G2" s="52" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="53" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E5" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>262</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="D6" s="62" t="n">
+        <v>295</v>
+      </c>
+      <c r="D6" s="61" t="n">
         <v>7619042.4</v>
       </c>
-      <c r="E6" s="67" t="n">
+      <c r="E6" s="66" t="n">
         <f aca="false">IFERROR(F6/D6,0)</f>
         <v>0.10284668266065</v>
       </c>
@@ -3722,15 +3716,15 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="D7" s="62" t="n">
+        <v>297</v>
+      </c>
+      <c r="D7" s="61" t="n">
         <v>2959722.4</v>
       </c>
-      <c r="E7" s="67" t="n">
+      <c r="E7" s="66" t="n">
         <f aca="false">IFERROR(F7/D7,0)</f>
         <v>0.172561522794754</v>
       </c>
@@ -3740,7 +3734,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="13" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
@@ -3751,7 +3745,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -3762,7 +3756,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
@@ -3773,11 +3767,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="C11" s="61"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
+        <v>301</v>
+      </c>
+      <c r="C11" s="60"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="60"/>
       <c r="F11" s="49" t="n">
         <f aca="false">SUM(F6:F10)</f>
         <v>1618616.16219</v>
@@ -3785,10 +3779,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="34" t="s">
-        <v>304</v>
-      </c>
-      <c r="F13" s="68" t="s">
-        <v>305</v>
+        <v>302</v>
+      </c>
+      <c r="F13" s="67" t="s">
+        <v>303</v>
       </c>
       <c r="G13" s="15" t="n">
         <v>0.12</v>
@@ -3799,36 +3793,36 @@
         <v>44</v>
       </c>
       <c r="C14" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="E14" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="F14" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="G14" s="19" t="s">
         <v>308</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="61"/>
+        <v>309</v>
+      </c>
+      <c r="C15" s="60"/>
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="60"/>
+      <c r="G15" s="60"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="C16" s="62" t="n">
+        <v>310</v>
+      </c>
+      <c r="C16" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="14" t="n">
@@ -3848,9 +3842,9 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C17" s="62" t="n">
+        <v>311</v>
+      </c>
+      <c r="C17" s="61" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="14" t="n">
@@ -3870,9 +3864,9 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="C18" s="62" t="n">
+        <v>310</v>
+      </c>
+      <c r="C18" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D18" s="14" t="n">
@@ -3892,9 +3886,9 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="C19" s="62" t="n">
+        <v>312</v>
+      </c>
+      <c r="C19" s="61" t="n">
         <v>8</v>
       </c>
       <c r="D19" s="14" t="n">
@@ -3914,9 +3908,9 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="C20" s="62" t="n">
+        <v>310</v>
+      </c>
+      <c r="C20" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D20" s="14" t="n">
@@ -3936,9 +3930,9 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="C21" s="62" t="n">
+        <v>313</v>
+      </c>
+      <c r="C21" s="61" t="n">
         <v>12</v>
       </c>
       <c r="D21" s="14" t="n">
@@ -3958,9 +3952,9 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="C22" s="62" t="n">
+        <v>314</v>
+      </c>
+      <c r="C22" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="14" t="n">
@@ -3980,9 +3974,9 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="C23" s="62" t="n">
+        <v>315</v>
+      </c>
+      <c r="C23" s="61" t="n">
         <v>8</v>
       </c>
       <c r="D23" s="14" t="n">
@@ -4002,9 +3996,9 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C24" s="62" t="n">
+        <v>316</v>
+      </c>
+      <c r="C24" s="61" t="n">
         <v>8</v>
       </c>
       <c r="D24" s="14" t="n">
@@ -4024,9 +4018,9 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="C25" s="62" t="n">
+        <v>317</v>
+      </c>
+      <c r="C25" s="61" t="n">
         <v>12</v>
       </c>
       <c r="D25" s="14" t="n">
@@ -4046,9 +4040,9 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C26" s="62" t="n">
+        <v>318</v>
+      </c>
+      <c r="C26" s="61" t="n">
         <v>10</v>
       </c>
       <c r="D26" s="14" t="n">
@@ -4068,9 +4062,9 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="C27" s="62" t="n">
+        <v>319</v>
+      </c>
+      <c r="C27" s="61" t="n">
         <v>8</v>
       </c>
       <c r="D27" s="14" t="n">
@@ -4092,7 +4086,7 @@
       <c r="B28" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="C28" s="69" t="n">
+      <c r="C28" s="68" t="n">
         <f aca="false">SUM(C16:C27)</f>
         <v>110</v>
       </c>
@@ -4109,32 +4103,32 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="61"/>
+        <v>320</v>
+      </c>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
       <c r="F29" s="49" t="n">
         <f aca="false">F28+G28</f>
         <v>1808303.85738393</v>
       </c>
-      <c r="G29" s="61"/>
+      <c r="G29" s="60"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="11" t="s">
-        <v>323</v>
-      </c>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
+        <v>321</v>
+      </c>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="C32" s="62" t="n">
+        <v>322</v>
+      </c>
+      <c r="C32" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="14" t="n">
@@ -4154,9 +4148,9 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="C33" s="62" t="n">
+        <v>323</v>
+      </c>
+      <c r="C33" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="14" t="n">
@@ -4176,9 +4170,9 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="C34" s="62" t="n">
+        <v>324</v>
+      </c>
+      <c r="C34" s="61" t="n">
         <v>3</v>
       </c>
       <c r="D34" s="14" t="n">
@@ -4198,9 +4192,9 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="C35" s="62" t="n">
+        <v>325</v>
+      </c>
+      <c r="C35" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="14" t="n">
@@ -4220,9 +4214,9 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="C36" s="62" t="n">
+        <v>326</v>
+      </c>
+      <c r="C36" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D36" s="14" t="n">
@@ -4242,9 +4236,9 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="C37" s="62" t="n">
+        <v>327</v>
+      </c>
+      <c r="C37" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D37" s="14" t="n">
@@ -4264,9 +4258,9 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="C38" s="62" t="n">
+        <v>328</v>
+      </c>
+      <c r="C38" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D38" s="14" t="n">
@@ -4286,9 +4280,9 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="C39" s="62" t="n">
+        <v>329</v>
+      </c>
+      <c r="C39" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="14" t="n">
@@ -4308,9 +4302,9 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="C40" s="62" t="n">
+        <v>330</v>
+      </c>
+      <c r="C40" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D40" s="14" t="n">
@@ -4330,9 +4324,9 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="C41" s="62" t="n">
+        <v>331</v>
+      </c>
+      <c r="C41" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D41" s="14" t="n">
@@ -4352,9 +4346,9 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="C42" s="62" t="n">
+        <v>332</v>
+      </c>
+      <c r="C42" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D42" s="14" t="n">
@@ -4374,9 +4368,9 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="C43" s="62" t="n">
+        <v>333</v>
+      </c>
+      <c r="C43" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D43" s="14" t="n">
@@ -4396,9 +4390,9 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="C44" s="62" t="n">
+        <v>334</v>
+      </c>
+      <c r="C44" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D44" s="14" t="n">
@@ -4418,9 +4412,9 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="C45" s="62" t="n">
+        <v>335</v>
+      </c>
+      <c r="C45" s="61" t="n">
         <v>2</v>
       </c>
       <c r="D45" s="14" t="n">
@@ -4440,9 +4434,9 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="C46" s="62" t="n">
+        <v>336</v>
+      </c>
+      <c r="C46" s="61" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="14" t="n">
@@ -4462,9 +4456,9 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="C47" s="62" t="n">
+        <v>337</v>
+      </c>
+      <c r="C47" s="61" t="n">
         <v>2</v>
       </c>
       <c r="D47" s="14" t="n">
@@ -4484,9 +4478,9 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="C48" s="62" t="n">
+        <v>338</v>
+      </c>
+      <c r="C48" s="61" t="n">
         <v>5</v>
       </c>
       <c r="D48" s="14" t="n">
@@ -4506,9 +4500,9 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="C49" s="62" t="n">
+        <v>339</v>
+      </c>
+      <c r="C49" s="61" t="n">
         <v>3</v>
       </c>
       <c r="D49" s="14" t="n">
@@ -4530,7 +4524,7 @@
       <c r="B50" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="C50" s="69" t="n">
+      <c r="C50" s="68" t="n">
         <f aca="false">SUM(C32:C49)</f>
         <v>28</v>
       </c>
@@ -4547,36 +4541,36 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="C51" s="61"/>
-      <c r="D51" s="61"/>
-      <c r="E51" s="61"/>
+        <v>320</v>
+      </c>
+      <c r="C51" s="60"/>
+      <c r="D51" s="60"/>
+      <c r="E51" s="60"/>
       <c r="F51" s="49" t="n">
         <f aca="false">F50+G50</f>
         <v>393814.950996336</v>
       </c>
-      <c r="G51" s="61"/>
+      <c r="G51" s="60"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="C53" s="70" t="n">
+        <v>340</v>
+      </c>
+      <c r="C53" s="69" t="n">
         <f aca="false">C28+C50</f>
         <v>138</v>
       </c>
-      <c r="D53" s="65"/>
-      <c r="E53" s="65"/>
+      <c r="D53" s="64"/>
+      <c r="E53" s="64"/>
       <c r="F53" s="17" t="n">
         <f aca="false">F29+F51</f>
         <v>2202118.80838026</v>
       </c>
-      <c r="G53" s="65"/>
+      <c r="G53" s="64"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>
@@ -4606,10 +4600,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4617,7 +4611,7 @@
         <v>44</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>46</v>
@@ -4654,9 +4648,9 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="C6" s="61"/>
+        <v>345</v>
+      </c>
+      <c r="C6" s="60"/>
       <c r="D6" s="49" t="n">
         <f aca="false">SUM(D7:D11)</f>
         <v>354260.87242687</v>
@@ -4688,10 +4682,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D7" s="14" t="n">
         <f aca="false">CostSold!D35</f>
@@ -4724,7 +4718,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C8" s="20"/>
       <c r="D8" s="14" t="n">
@@ -4758,7 +4752,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C9" s="20"/>
       <c r="D9" s="14" t="n">
@@ -4792,7 +4786,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="14" t="n">
@@ -4826,10 +4820,10 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>222423.754154549</v>
@@ -4855,78 +4849,78 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="C13" s="61"/>
+        <v>353</v>
+      </c>
+      <c r="C13" s="60"/>
       <c r="D13" s="49" t="n">
         <f aca="false">D14+D15</f>
-        <v>9625.47122569664</v>
+        <v>0</v>
       </c>
       <c r="E13" s="49" t="n">
         <f aca="false">E14+E15</f>
-        <v>1099291.04294347</v>
+        <v>931388.412948486</v>
       </c>
       <c r="F13" s="49" t="n">
         <f aca="false">F14+F15</f>
-        <v>1961140.4913647</v>
+        <v>1974051.62599893</v>
       </c>
       <c r="G13" s="49" t="n">
         <f aca="false">G14+G15</f>
-        <v>2665862.70100625</v>
+        <v>2678773.83564048</v>
       </c>
       <c r="H13" s="49" t="n">
         <f aca="false">H14+H15</f>
-        <v>2774161.72874966</v>
+        <v>2787072.86338389</v>
       </c>
       <c r="I13" s="49" t="n">
         <f aca="false">I14+I15</f>
-        <v>2873669.02131528</v>
+        <v>2886580.15594952</v>
       </c>
       <c r="J13" s="49" t="n">
         <f aca="false">J14+J15</f>
-        <v>2975205.15153269</v>
+        <v>2988116.28616693</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C14" s="20"/>
       <c r="D14" s="14" t="n">
         <f aca="false">ProfLoss!D21</f>
-        <v>9625.47122569664</v>
+        <v>0</v>
       </c>
       <c r="E14" s="14" t="n">
         <f aca="false">ProfLoss!E21</f>
-        <v>1099291.04294347</v>
+        <v>931388.412948486</v>
       </c>
       <c r="F14" s="14" t="n">
         <f aca="false">ProfLoss!F21</f>
-        <v>1961140.4913647</v>
+        <v>1974051.62599893</v>
       </c>
       <c r="G14" s="14" t="n">
         <f aca="false">ProfLoss!G21</f>
-        <v>2665862.70100625</v>
+        <v>2678773.83564048</v>
       </c>
       <c r="H14" s="14" t="n">
         <f aca="false">ProfLoss!H21</f>
-        <v>2774161.72874966</v>
+        <v>2787072.86338389</v>
       </c>
       <c r="I14" s="14" t="n">
         <f aca="false">ProfLoss!I21</f>
-        <v>2873669.02131528</v>
+        <v>2886580.15594952</v>
       </c>
       <c r="J14" s="14" t="n">
         <f aca="false">ProfLoss!J21</f>
-        <v>2975205.15153269</v>
+        <v>2988116.28616693</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D15" s="14" t="n">
         <f aca="false">MAX(0,D22)</f>
@@ -4959,46 +4953,46 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="39" t="s">
-        <v>358</v>
-      </c>
-      <c r="C16" s="63"/>
+        <v>356</v>
+      </c>
+      <c r="C16" s="62"/>
       <c r="D16" s="17" t="n">
         <f aca="false">D6+D13</f>
-        <v>363886.343652567</v>
+        <v>354260.87242687</v>
       </c>
       <c r="E16" s="17" t="n">
         <f aca="false">E6+E13</f>
-        <v>1841094.06806761</v>
+        <v>1673191.43807263</v>
       </c>
       <c r="F16" s="17" t="n">
         <f aca="false">F6+F13</f>
-        <v>2697307.06432187</v>
+        <v>2710218.1989561</v>
       </c>
       <c r="G16" s="17" t="n">
         <f aca="false">G6+G13</f>
-        <v>3396523.89053806</v>
+        <v>3409435.02517229</v>
       </c>
       <c r="H16" s="17" t="n">
         <f aca="false">H6+H13</f>
-        <v>3499431.38329409</v>
+        <v>3512342.51792832</v>
       </c>
       <c r="I16" s="17" t="n">
         <f aca="false">I6+I13</f>
-        <v>3593661.33646195</v>
+        <v>3606572.47109619</v>
       </c>
       <c r="J16" s="17" t="n">
         <f aca="false">J6+J13</f>
-        <v>3690036.83517422</v>
+        <v>3702947.96980845</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="34" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C19" s="20"/>
       <c r="D19" s="14" t="n">
@@ -5025,7 +5019,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C20" s="20"/>
       <c r="D20" s="14" t="n">
@@ -5052,7 +5046,7 @@
     </row>
     <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="14" t="n">
@@ -5079,7 +5073,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="29" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="22" t="n">
@@ -5113,46 +5107,46 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="34" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C25" s="20"/>
       <c r="D25" s="14" t="n">
         <f aca="false">ProfLoss!D20</f>
-        <v>64169.8081713109</v>
+        <v>-1205425.09752808</v>
       </c>
       <c r="E25" s="14" t="n">
         <f aca="false">ProfLoss!E20</f>
-        <v>7328606.95295645</v>
+        <v>7414681.18385132</v>
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">ProfLoss!F20</f>
-        <v>13074269.9424313</v>
+        <v>13160344.1733262</v>
       </c>
       <c r="G25" s="14" t="n">
         <f aca="false">ProfLoss!G20</f>
-        <v>17772418.0067083</v>
+        <v>17858492.2376032</v>
       </c>
       <c r="H25" s="14" t="n">
         <f aca="false">ProfLoss!H20</f>
-        <v>18494411.5249977</v>
+        <v>18580485.7558926</v>
       </c>
       <c r="I25" s="14" t="n">
         <f aca="false">ProfLoss!I20</f>
-        <v>19157793.4754352</v>
+        <v>19243867.7063301</v>
       </c>
       <c r="J25" s="14" t="n">
         <f aca="false">ProfLoss!J20</f>
-        <v>19834701.010218</v>
+        <v>19920775.2411128</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C26" s="20"/>
       <c r="D26" s="14" t="n">
@@ -5179,44 +5173,44 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="14" t="n">
         <f aca="false">D25+D26</f>
-        <v>64169.8081713109</v>
+        <v>-1205425.09752808</v>
       </c>
       <c r="E27" s="14" t="n">
         <f aca="false">E25+E26</f>
-        <v>7328606.95295645</v>
+        <v>7414681.18385132</v>
       </c>
       <c r="F27" s="14" t="n">
         <f aca="false">F25+F26</f>
-        <v>13074269.9424313</v>
+        <v>13160344.1733262</v>
       </c>
       <c r="G27" s="14" t="n">
         <f aca="false">G25+G26</f>
-        <v>17772418.0067083</v>
+        <v>17858492.2376032</v>
       </c>
       <c r="H27" s="14" t="n">
         <f aca="false">H25+H26</f>
-        <v>18494411.5249977</v>
+        <v>18580485.7558926</v>
       </c>
       <c r="I27" s="14" t="n">
         <f aca="false">I25+I26</f>
-        <v>19157793.4754352</v>
+        <v>19243867.7063301</v>
       </c>
       <c r="J27" s="14" t="n">
         <f aca="false">J25+J26</f>
-        <v>19834701.010218</v>
+        <v>19920775.2411128</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D28" s="15" t="n">
         <v>0.15</v>
@@ -5242,36 +5236,36 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="29" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C29" s="20"/>
       <c r="D29" s="22" t="n">
-        <f aca="false">D27*D28</f>
-        <v>9625.47122569664</v>
+        <f aca="false">MAX(0,MIN(D27,SUM($D27:D27)))*D28</f>
+        <v>0</v>
       </c>
       <c r="E29" s="22" t="n">
-        <f aca="false">E27*E28</f>
-        <v>1099291.04294347</v>
+        <f aca="false">MAX(0,MIN(E27,SUM($D27:E27)))*E28</f>
+        <v>931388.412948486</v>
       </c>
       <c r="F29" s="22" t="n">
-        <f aca="false">F27*F28</f>
-        <v>1961140.4913647</v>
+        <f aca="false">MAX(0,MIN(F27,SUM($D27:F27)))*F28</f>
+        <v>1974051.62599893</v>
       </c>
       <c r="G29" s="22" t="n">
-        <f aca="false">G27*G28</f>
-        <v>2665862.70100625</v>
+        <f aca="false">MAX(0,MIN(G27,SUM($D27:G27)))*G28</f>
+        <v>2678773.83564048</v>
       </c>
       <c r="H29" s="22" t="n">
-        <f aca="false">H27*H28</f>
-        <v>2774161.72874966</v>
+        <f aca="false">MAX(0,MIN(H27,SUM($D27:H27)))*H28</f>
+        <v>2787072.86338389</v>
       </c>
       <c r="I29" s="22" t="n">
-        <f aca="false">I27*I28</f>
-        <v>2873669.02131528</v>
+        <f aca="false">MAX(0,MIN(I27,SUM($D27:I27)))*I28</f>
+        <v>2886580.15594952</v>
       </c>
       <c r="J29" s="22" t="n">
-        <f aca="false">J27*J28</f>
-        <v>2975205.15153269</v>
+        <f aca="false">MAX(0,MIN(J27,SUM($D27:J27)))*J28</f>
+        <v>2988116.28616693</v>
       </c>
     </row>
   </sheetData>
@@ -5314,40 +5308,40 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="H2" s="52" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="53" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="E5" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="F5" s="19" t="s">
         <v>375</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="G5" s="19" t="s">
         <v>376</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>377</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="26" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">C7+C8</f>
@@ -5372,7 +5366,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">F7+G7</f>
@@ -5396,7 +5390,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="13" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">F8+G8</f>
@@ -5420,7 +5414,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">F9+G9</f>
@@ -5445,7 +5439,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C10" s="14" t="n">
         <f aca="false">F10+G10</f>
@@ -5469,7 +5463,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C11" s="14" t="n">
         <f aca="false">F11+G11</f>
@@ -5493,7 +5487,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C12" s="14" t="n">
         <f aca="false">F12+G12</f>
@@ -5517,7 +5511,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C13" s="14" t="n">
         <f aca="false">F13+G13</f>
@@ -5541,7 +5535,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C14" s="14" t="n">
         <f aca="false">F14+G14</f>
@@ -5565,7 +5559,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C15" s="14" t="n">
         <f aca="false">F15+G15</f>
@@ -5588,7 +5582,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">F16+G16</f>
@@ -5612,7 +5606,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C17" s="14" t="n">
         <f aca="false">F17+G17</f>
@@ -5636,7 +5630,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="13" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C18" s="14" t="n">
         <f aca="false">F18+G18</f>
@@ -5660,7 +5654,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="13" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C19" s="14" t="n">
         <f aca="false">F19+G19</f>
@@ -5684,7 +5678,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="13" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C20" s="14" t="n">
         <f aca="false">F20+G20</f>
@@ -5708,11 +5702,11 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="13" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C21" s="14" t="n">
         <f aca="false">F21+G21</f>
-        <v>2835492.57919845</v>
+        <v>2749418.34830358</v>
       </c>
       <c r="D21" s="15" t="n">
         <f aca="false">IFERROR(F21/C21,0)</f>
@@ -5723,8 +5717,8 @@
         <v>0</v>
       </c>
       <c r="F21" s="14" t="n">
-        <f aca="false">Depreciate!J18</f>
-        <v>2835492.57919845</v>
+        <f aca="false">Depreciate!J17</f>
+        <v>2749418.34830358</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>0</v>
@@ -5736,19 +5730,19 @@
       </c>
       <c r="C22" s="17" t="n">
         <f aca="false">SUM(C6:C21)-C6</f>
-        <v>40732107.5637365</v>
+        <v>40646033.3328416</v>
       </c>
       <c r="D22" s="18" t="n">
         <f aca="false">IFERROR(F22/C22,0)</f>
-        <v>0.240558189565465</v>
+        <v>0.238949954655867</v>
       </c>
       <c r="E22" s="18" t="n">
         <f aca="false">IFERROR(G22/C22,0)</f>
-        <v>0.759441810434535</v>
+        <v>0.761050045344133</v>
       </c>
       <c r="F22" s="17" t="n">
         <f aca="false">SUM(F6:F21)-F6</f>
-        <v>9798442.05271821</v>
+        <v>9712367.82182333</v>
       </c>
       <c r="G22" s="17" t="n">
         <f aca="false">SUM(G6:G21)-G6</f>
@@ -5757,16 +5751,16 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="13" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C23" s="14" t="n">
         <f aca="false">C22-C24</f>
-        <v>39146523.7254355</v>
+        <v>39060449.4945407</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="13" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>1585583.83830092</v>
@@ -5774,7 +5768,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C26" s="14" t="n">
         <f aca="false">SalePlan!G18</f>
@@ -5783,20 +5777,20 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="C27" s="71" t="n">
+        <v>395</v>
+      </c>
+      <c r="C27" s="70" t="n">
         <f aca="false">IFERROR(C22/C26,0)</f>
-        <v>0.691343818912509</v>
+        <v>0.689882885730898</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="13" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C28" s="14" t="n">
         <f aca="false">IFERROR(C22/ProdPlan!G17,0)</f>
-        <v>20539.9242405646</v>
+        <v>20496.5197057298</v>
       </c>
     </row>
   </sheetData>
@@ -5826,10 +5820,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5874,10 +5868,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D6" s="15" t="n">
         <f aca="false">ProdPlan!D13</f>
@@ -5910,12 +5904,12 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="34" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>34</v>
@@ -5944,7 +5938,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>34</v>
@@ -5973,7 +5967,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>34</v>
@@ -6002,7 +5996,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>34</v>
@@ -6031,7 +6025,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>34</v>
@@ -6060,7 +6054,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>34</v>
@@ -6089,7 +6083,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>34</v>
@@ -6118,43 +6112,43 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D16" s="14" t="n">
-        <f aca="false">Depreciate!$G$19</f>
-        <v>566139.040861338</v>
+        <f aca="false">Depreciate!$G$18</f>
+        <v>544620.483137619</v>
       </c>
       <c r="E16" s="14" t="n">
-        <f aca="false">Depreciate!$H$19</f>
-        <v>2323012.62002274</v>
+        <f aca="false">Depreciate!$H$18</f>
+        <v>2236938.38912786</v>
       </c>
       <c r="F16" s="14" t="n">
-        <f aca="false">Depreciate!$I$19</f>
-        <v>2376972.42609416</v>
+        <f aca="false">Depreciate!$I$18</f>
+        <v>2290898.19519929</v>
       </c>
       <c r="G16" s="14" t="n">
-        <f aca="false">Depreciate!$J$19</f>
-        <v>2430932.23216559</v>
+        <f aca="false">Depreciate!$J$18</f>
+        <v>2344858.00127072</v>
       </c>
       <c r="H16" s="14" t="n">
-        <f aca="false">Depreciate!$K$19</f>
-        <v>2484892.03823702</v>
+        <f aca="false">Depreciate!$K$18</f>
+        <v>2398817.80734215</v>
       </c>
       <c r="I16" s="14" t="n">
-        <f aca="false">Depreciate!$L$19</f>
-        <v>2538851.84430845</v>
+        <f aca="false">Depreciate!$L$18</f>
+        <v>2452777.61341358</v>
       </c>
       <c r="J16" s="14" t="n">
-        <f aca="false">Depreciate!$M$19</f>
-        <v>2592811.65037988</v>
+        <f aca="false">Depreciate!$M$18</f>
+        <v>2506737.419485</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>34</v>
@@ -6183,7 +6177,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>34</v>
@@ -6212,7 +6206,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>34</v>
@@ -6240,44 +6234,44 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="72" t="s">
-        <v>414</v>
-      </c>
-      <c r="C20" s="60" t="s">
+      <c r="B20" s="71" t="s">
+        <v>412</v>
+      </c>
+      <c r="C20" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="49" t="n">
         <f aca="false">SUM(D9:D19)</f>
-        <v>6561141.26004277</v>
+        <v>6539622.70231905</v>
       </c>
       <c r="E20" s="49" t="n">
         <f aca="false">SUM(E9:E19)</f>
-        <v>22874492.013103</v>
+        <v>22788417.7822082</v>
       </c>
       <c r="F20" s="49" t="n">
         <f aca="false">SUM(F9:F19)</f>
-        <v>29200927.4025167</v>
+        <v>29114853.1716218</v>
       </c>
       <c r="G20" s="49" t="n">
         <f aca="false">SUM(G9:G19)</f>
-        <v>34306434.0714228</v>
+        <v>34220359.8405279</v>
       </c>
       <c r="H20" s="49" t="n">
         <f aca="false">SUM(H9:H19)</f>
-        <v>35061654.9179578</v>
+        <v>34975580.6870629</v>
       </c>
       <c r="I20" s="49" t="n">
         <f aca="false">SUM(I9:I19)</f>
-        <v>35832303.5073831</v>
+        <v>35746229.2764882</v>
       </c>
       <c r="J20" s="49" t="n">
         <f aca="false">SUM(J9:J19)</f>
-        <v>36618719.2500422</v>
+        <v>36532645.0191474</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>34</v>
@@ -6305,47 +6299,47 @@
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="72" t="s">
-        <v>416</v>
-      </c>
-      <c r="C22" s="60" t="s">
+      <c r="B22" s="71" t="s">
+        <v>414</v>
+      </c>
+      <c r="C22" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="49" t="n">
         <f aca="false">D20+D21</f>
-        <v>3983085.34769568</v>
+        <v>3961566.78997196</v>
       </c>
       <c r="E22" s="49" t="n">
         <f aca="false">E20+E21</f>
-        <v>22748393.2278882</v>
+        <v>22662318.9969933</v>
       </c>
       <c r="F22" s="49" t="n">
         <f aca="false">F20+F21</f>
-        <v>28767725.6070918</v>
+        <v>28681651.3761969</v>
       </c>
       <c r="G22" s="49" t="n">
         <f aca="false">G20+G21</f>
-        <v>33957554.4079507</v>
+        <v>33871480.1770559</v>
       </c>
       <c r="H22" s="49" t="n">
         <f aca="false">H20+H21</f>
-        <v>35013223.0766929</v>
+        <v>34927148.845798</v>
       </c>
       <c r="I22" s="49" t="n">
         <f aca="false">I20+I21</f>
-        <v>35782806.1656104</v>
+        <v>35696731.9347155</v>
       </c>
       <c r="J22" s="49" t="n">
         <f aca="false">J20+J21</f>
-        <v>36568132.9667505</v>
+        <v>36482058.7358556</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D23" s="15" t="n">
         <v>0.038868172520961</v>
@@ -6371,84 +6365,84 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="14" t="n">
         <f aca="false">D22*D23</f>
-        <v>154815.248459948</v>
+        <v>153978.86144594</v>
       </c>
       <c r="E24" s="14" t="n">
         <f aca="false">E22*E23</f>
-        <v>1123057.22606462</v>
+        <v>1118807.85838331</v>
       </c>
       <c r="F24" s="14" t="n">
         <f aca="false">F22*F23</f>
-        <v>1434045.71414757</v>
+        <v>1429754.98975735</v>
       </c>
       <c r="G24" s="14" t="n">
         <f aca="false">G22*G23</f>
-        <v>1689151.42823444</v>
+        <v>1684869.83574095</v>
       </c>
       <c r="H24" s="14" t="n">
         <f aca="false">H22*H23</f>
-        <v>1717864.5220173</v>
+        <v>1713641.43557964</v>
       </c>
       <c r="I24" s="14" t="n">
         <f aca="false">I22*I23</f>
-        <v>1731824.22667559</v>
+        <v>1727658.38686788</v>
       </c>
       <c r="J24" s="14" t="n">
         <f aca="false">J22*J23</f>
-        <v>1746035.29446564</v>
+        <v>1741925.46897296</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D25" s="14" t="n">
         <f aca="false">D22-D24</f>
-        <v>3828270.09923573</v>
+        <v>3807587.92852602</v>
       </c>
       <c r="E25" s="14" t="n">
         <f aca="false">E22-E24</f>
-        <v>21625336.0018236</v>
+        <v>21543511.13861</v>
       </c>
       <c r="F25" s="14" t="n">
         <f aca="false">F22-F24</f>
-        <v>27333679.8929442</v>
+        <v>27251896.3864395</v>
       </c>
       <c r="G25" s="14" t="n">
         <f aca="false">G22-G24</f>
-        <v>32268402.9797163</v>
+        <v>32186610.3413149</v>
       </c>
       <c r="H25" s="14" t="n">
         <f aca="false">H22-H24</f>
-        <v>33295358.5546756</v>
+        <v>33213507.4102184</v>
       </c>
       <c r="I25" s="14" t="n">
         <f aca="false">I22-I24</f>
-        <v>34050981.9389348</v>
+        <v>33969073.5478476</v>
       </c>
       <c r="J25" s="14" t="n">
         <f aca="false">J22-J24</f>
-        <v>34822097.6722849</v>
+        <v>34740133.2668827</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="34" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>34</v>
@@ -6477,43 +6471,43 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D29" s="14" t="n">
-        <f aca="false">Depreciate!$G$20</f>
+        <f aca="false">Depreciate!$G$19</f>
         <v>101140.086758214</v>
       </c>
       <c r="E29" s="14" t="n">
-        <f aca="false">Depreciate!$H$20</f>
+        <f aca="false">Depreciate!$H$19</f>
         <v>404560.347032858</v>
       </c>
       <c r="F29" s="14" t="n">
-        <f aca="false">Depreciate!$I$20</f>
+        <f aca="false">Depreciate!$I$19</f>
         <v>404560.347032858</v>
       </c>
       <c r="G29" s="14" t="n">
-        <f aca="false">Depreciate!$J$20</f>
+        <f aca="false">Depreciate!$J$19</f>
         <v>404560.347032858</v>
       </c>
       <c r="H29" s="14" t="n">
-        <f aca="false">Depreciate!$K$20</f>
+        <f aca="false">Depreciate!$K$19</f>
         <v>404560.347032858</v>
       </c>
       <c r="I29" s="14" t="n">
-        <f aca="false">Depreciate!$L$20</f>
+        <f aca="false">Depreciate!$L$19</f>
         <v>404560.347032858</v>
       </c>
       <c r="J29" s="14" t="n">
-        <f aca="false">Depreciate!$M$20</f>
+        <f aca="false">Depreciate!$M$19</f>
         <v>404560.347032858</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="7" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C30" s="20" t="s">
         <v>34</v>
@@ -6542,7 +6536,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C31" s="20" t="s">
         <v>34</v>
@@ -6570,10 +6564,10 @@
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="72" t="s">
-        <v>425</v>
-      </c>
-      <c r="C32" s="60" t="s">
+      <c r="B32" s="71" t="s">
+        <v>423</v>
+      </c>
+      <c r="C32" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="49" t="n">
@@ -6607,12 +6601,12 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="34" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C35" s="20" t="s">
         <v>34</v>
@@ -6641,7 +6635,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C36" s="20" t="s">
         <v>34</v>
@@ -6670,7 +6664,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C37" s="20" t="s">
         <v>34</v>
@@ -6699,7 +6693,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="7" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C38" s="20" t="s">
         <v>34</v>
@@ -6728,7 +6722,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="7" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C39" s="20" t="s">
         <v>34</v>
@@ -6756,10 +6750,10 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="72" t="s">
-        <v>429</v>
-      </c>
-      <c r="C40" s="60" t="s">
+      <c r="B40" s="71" t="s">
+        <v>427</v>
+      </c>
+      <c r="C40" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D40" s="49" t="n">
@@ -6793,18 +6787,19 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="34" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C43" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>0</v>
+        <f aca="false">LOANS!$C$106</f>
+        <v>1291113.46342311</v>
       </c>
       <c r="E43" s="14" t="n">
         <f aca="false">LOANS!$D$106</f>
@@ -6833,74 +6828,74 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="39" t="s">
-        <v>432</v>
-      </c>
-      <c r="C45" s="63" t="s">
+        <v>430</v>
+      </c>
+      <c r="C45" s="62" t="s">
         <v>34</v>
       </c>
       <c r="D45" s="17" t="n">
         <f aca="false">D22+D32+D40+D43</f>
-        <v>8994063.59928899</v>
+        <v>10263658.5049884</v>
       </c>
       <c r="E45" s="17" t="n">
         <f aca="false">E22+E32+E40+E43</f>
-        <v>29449343.1647103</v>
+        <v>29363268.9338154</v>
       </c>
       <c r="F45" s="17" t="n">
         <f aca="false">F22+F32+F40+F43</f>
-        <v>35751441.8718188</v>
+        <v>35665367.6409239</v>
       </c>
       <c r="G45" s="17" t="n">
         <f aca="false">G22+G32+G40+G43</f>
-        <v>41144876.7596042</v>
+        <v>41058802.5287093</v>
       </c>
       <c r="H45" s="17" t="n">
         <f aca="false">H22+H32+H40+H43</f>
-        <v>42098292.3250023</v>
+        <v>42012218.0941074</v>
       </c>
       <c r="I45" s="17" t="n">
         <f aca="false">I22+I32+I40+I43</f>
-        <v>42767533.4145648</v>
+        <v>42681459.1836699</v>
       </c>
       <c r="J45" s="17" t="n">
         <f aca="false">J22+J32+J40+J43</f>
-        <v>43452994.969782</v>
+        <v>43366920.7388872</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D46" s="14" t="n">
         <f aca="false">IFERROR(D45/(ProdPlan!D21+ProdPlan!D22),0)</f>
-        <v>36283.3933216235</v>
+        <v>41405.1284321315</v>
       </c>
       <c r="E46" s="14" t="n">
         <f aca="false">IFERROR(E45/(ProdPlan!E21+ProdPlan!E22),0)</f>
-        <v>22920.2007194453</v>
+        <v>22853.2097975137</v>
       </c>
       <c r="F46" s="14" t="n">
         <f aca="false">IFERROR(F45/(ProdPlan!F21+ProdPlan!F22),0)</f>
-        <v>21419.7989177309</v>
+        <v>21368.2291733727</v>
       </c>
       <c r="G46" s="14" t="n">
         <f aca="false">IFERROR(G45/(ProdPlan!G21+ProdPlan!G22),0)</f>
-        <v>20878.5618104318</v>
+        <v>20834.8842911012</v>
       </c>
       <c r="H46" s="14" t="n">
         <f aca="false">IFERROR(H45/(ProdPlan!H21+ProdPlan!H22),0)</f>
-        <v>21228.8483639016</v>
+        <v>21185.4438290667</v>
       </c>
       <c r="I46" s="14" t="n">
         <f aca="false">IFERROR(I45/(ProdPlan!I21+ProdPlan!I22),0)</f>
-        <v>21566.325653943</v>
+        <v>21522.9211191082</v>
       </c>
       <c r="J46" s="14" t="n">
         <f aca="false">IFERROR(J45/(ProdPlan!J21+ProdPlan!J22),0)</f>
-        <v>21911.9824160428</v>
+        <v>21868.577881208</v>
       </c>
     </row>
   </sheetData>
@@ -6942,46 +6937,46 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H2" s="52" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="59" t="n">
+      <c r="C5" s="72" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$28</f>
         <v>84</v>
       </c>
       <c r="D5" s="73" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="C6" s="59" t="n">
+        <v>435</v>
+      </c>
+      <c r="C6" s="72" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$29</f>
         <v>12</v>
       </c>
       <c r="D6" s="73" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>438</v>
-      </c>
-      <c r="C7" s="59" t="n">
+        <v>436</v>
+      </c>
+      <c r="C7" s="72" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$30</f>
         <v>12</v>
       </c>
       <c r="D7" s="73" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6993,12 +6988,12 @@
         <v>0.07</v>
       </c>
       <c r="D8" s="73" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$26</f>
@@ -7010,7 +7005,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C10" s="74" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$31</f>
@@ -7020,31 +7015,31 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="C11" s="59" t="n">
+        <v>440</v>
+      </c>
+      <c r="C11" s="72" t="n">
         <f aca="false">ИНФОРМАЦИЯ!$C$32</f>
         <v>360</v>
       </c>
       <c r="D11" s="73" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>444</v>
-      </c>
-      <c r="C12" s="59" t="n">
+        <v>442</v>
+      </c>
+      <c r="C12" s="72" t="n">
         <f aca="false">C5-C6</f>
         <v>72</v>
       </c>
       <c r="D12" s="73" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C13" s="30" t="n">
         <f aca="false">C9/C12</f>
@@ -7056,28 +7051,28 @@
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>447</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>449</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>128</v>
       </c>
       <c r="E15" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="G15" s="19" t="s">
         <v>450</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="H15" s="19" t="s">
         <v>451</v>
-      </c>
-      <c r="G15" s="19" t="s">
-        <v>452</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9871,7 +9866,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B102" s="34" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9902,7 +9897,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B104" s="13" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C104" s="14" t="n">
         <f aca="false">$C$9</f>
@@ -9962,7 +9957,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B106" s="13" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C106" s="14" t="n">
         <f aca="false">SUMIF($H$16:$H$99,1,$E$16:$E$99)</f>
@@ -9995,7 +9990,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B107" s="26" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C107" s="14" t="n">
         <f aca="false">C105+C106</f>
@@ -10028,7 +10023,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B108" s="26" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C108" s="14" t="n">
         <f aca="false">$C$9-SUM($C$105:C105)</f>
@@ -10086,10 +10081,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10134,7 +10129,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="29" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>34</v>
@@ -10170,7 +10165,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>34</v>
@@ -10206,7 +10201,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>34</v>
@@ -10242,7 +10237,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>34</v>
@@ -10277,10 +10272,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="72" t="s">
-        <v>464</v>
-      </c>
-      <c r="C10" s="60" t="s">
+      <c r="B10" s="71" t="s">
+        <v>462</v>
+      </c>
+      <c r="C10" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="49" t="n">
@@ -10314,151 +10309,151 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">CostSold!D22</f>
-        <v>3983085.34769568</v>
+        <v>3961566.78997196</v>
       </c>
       <c r="E11" s="14" t="n">
         <f aca="false">CostSold!E22</f>
-        <v>22748393.2278882</v>
+        <v>22662318.9969933</v>
       </c>
       <c r="F11" s="14" t="n">
         <f aca="false">CostSold!F22</f>
-        <v>28767725.6070918</v>
+        <v>28681651.3761969</v>
       </c>
       <c r="G11" s="14" t="n">
         <f aca="false">CostSold!G22</f>
-        <v>33957554.4079507</v>
+        <v>33871480.1770559</v>
       </c>
       <c r="H11" s="14" t="n">
         <f aca="false">CostSold!H22</f>
-        <v>35013223.0766929</v>
+        <v>34927148.845798</v>
       </c>
       <c r="I11" s="14" t="n">
         <f aca="false">CostSold!I22</f>
-        <v>35782806.1656104</v>
+        <v>35696731.9347155</v>
       </c>
       <c r="J11" s="14" t="n">
         <f aca="false">CostSold!J22</f>
-        <v>36568132.9667505</v>
+        <v>36482058.7358556</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="14" t="n">
         <f aca="false">CostSold!D24</f>
-        <v>154815.248459948</v>
+        <v>153978.86144594</v>
       </c>
       <c r="E12" s="14" t="n">
         <f aca="false">CostSold!E24</f>
-        <v>1123057.22606462</v>
+        <v>1118807.85838331</v>
       </c>
       <c r="F12" s="14" t="n">
         <f aca="false">CostSold!F24</f>
-        <v>1434045.71414757</v>
+        <v>1429754.98975735</v>
       </c>
       <c r="G12" s="14" t="n">
         <f aca="false">CostSold!G24</f>
-        <v>1689151.42823444</v>
+        <v>1684869.83574095</v>
       </c>
       <c r="H12" s="14" t="n">
         <f aca="false">CostSold!H24</f>
-        <v>1717864.5220173</v>
+        <v>1713641.43557964</v>
       </c>
       <c r="I12" s="14" t="n">
         <f aca="false">CostSold!I24</f>
-        <v>1731824.22667559</v>
+        <v>1727658.38686788</v>
       </c>
       <c r="J12" s="14" t="n">
         <f aca="false">CostSold!J24</f>
-        <v>1746035.29446564</v>
+        <v>1741925.46897296</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">CostSold!D25</f>
-        <v>3828270.09923573</v>
+        <v>3807587.92852602</v>
       </c>
       <c r="E13" s="14" t="n">
         <f aca="false">CostSold!E25</f>
-        <v>21625336.0018236</v>
+        <v>21543511.13861</v>
       </c>
       <c r="F13" s="14" t="n">
         <f aca="false">CostSold!F25</f>
-        <v>27333679.8929442</v>
+        <v>27251896.3864395</v>
       </c>
       <c r="G13" s="14" t="n">
         <f aca="false">CostSold!G25</f>
-        <v>32268402.9797163</v>
+        <v>32186610.3413149</v>
       </c>
       <c r="H13" s="14" t="n">
         <f aca="false">CostSold!H25</f>
-        <v>33295358.5546756</v>
+        <v>33213507.4102184</v>
       </c>
       <c r="I13" s="14" t="n">
         <f aca="false">CostSold!I25</f>
-        <v>34050981.9389348</v>
+        <v>33969073.5478476</v>
       </c>
       <c r="J13" s="14" t="n">
         <f aca="false">CostSold!J25</f>
-        <v>34822097.6722849</v>
+        <v>34740133.2668827</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="72" t="s">
-        <v>467</v>
-      </c>
-      <c r="C14" s="60" t="s">
+      <c r="B14" s="71" t="s">
+        <v>465</v>
+      </c>
+      <c r="C14" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="49" t="n">
         <f aca="false">D10-D11</f>
-        <v>5075148.05976462</v>
+        <v>5096666.61748834</v>
       </c>
       <c r="E14" s="49" t="n">
         <f aca="false">E10-E11</f>
-        <v>14029556.8897786</v>
+        <v>14115631.1206734</v>
       </c>
       <c r="F14" s="49" t="n">
         <f aca="false">F10-F11</f>
-        <v>20057986.2071583</v>
+        <v>20144060.4380532</v>
       </c>
       <c r="G14" s="49" t="n">
         <f aca="false">G10-G11</f>
-        <v>24959740.3583618</v>
+        <v>25045814.5892566</v>
       </c>
       <c r="H14" s="49" t="n">
         <f aca="false">H10-H11</f>
-        <v>25579480.7733071</v>
+        <v>25665555.004202</v>
       </c>
       <c r="I14" s="49" t="n">
         <f aca="false">I10-I11</f>
-        <v>26142520.7243897</v>
+        <v>26228594.9552845</v>
       </c>
       <c r="J14" s="49" t="n">
         <f aca="false">J10-J11</f>
-        <v>26719563.0132495</v>
+        <v>26805637.2441444</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>34</v>
@@ -10494,7 +10489,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>34</v>
@@ -10529,51 +10524,51 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="72" t="s">
-        <v>470</v>
-      </c>
-      <c r="C17" s="60" t="s">
+      <c r="B17" s="71" t="s">
+        <v>468</v>
+      </c>
+      <c r="C17" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="49" t="n">
         <f aca="false">D14-D15-D16</f>
-        <v>64169.8081713109</v>
+        <v>85688.3658950306</v>
       </c>
       <c r="E17" s="49" t="n">
         <f aca="false">E14-E15-E16</f>
-        <v>8524115.1348034</v>
+        <v>8610189.36569828</v>
       </c>
       <c r="F17" s="49" t="n">
         <f aca="false">F14-F15-F16</f>
-        <v>14051104.3790082</v>
+        <v>14137178.6099031</v>
       </c>
       <c r="G17" s="49" t="n">
         <f aca="false">G14-G15-G16</f>
-        <v>18534066.8660481</v>
+        <v>18620141.096943</v>
       </c>
       <c r="H17" s="49" t="n">
         <f aca="false">H14-H15-H16</f>
-        <v>19040874.8071003</v>
+        <v>19126949.0379952</v>
       </c>
       <c r="I17" s="49" t="n">
         <f aca="false">I14-I15-I16</f>
-        <v>19490201.1502267</v>
+        <v>19576275.3811216</v>
       </c>
       <c r="J17" s="49" t="n">
         <f aca="false">J14-J15-J16</f>
-        <v>19950793.1378462</v>
+        <v>20036867.368741</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C18" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D18" s="14" t="n">
         <f aca="false">D19</f>
-        <v>0</v>
+        <v>1291113.46342311</v>
       </c>
       <c r="E18" s="14" t="n">
         <f aca="false">E19</f>
@@ -10602,14 +10597,14 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D19" s="14" t="n">
         <f aca="false">CostSold!D43</f>
-        <v>0</v>
+        <v>1291113.46342311</v>
       </c>
       <c r="E19" s="14" t="n">
         <f aca="false">CostSold!E43</f>
@@ -10637,188 +10632,188 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="72" t="s">
-        <v>473</v>
-      </c>
-      <c r="C20" s="60" t="s">
+      <c r="B20" s="71" t="s">
+        <v>471</v>
+      </c>
+      <c r="C20" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="49" t="n">
         <f aca="false">D17-D18</f>
-        <v>64169.8081713109</v>
+        <v>-1205425.09752808</v>
       </c>
       <c r="E20" s="49" t="n">
         <f aca="false">E17-E18</f>
-        <v>7328606.95295645</v>
+        <v>7414681.18385132</v>
       </c>
       <c r="F20" s="49" t="n">
         <f aca="false">F17-F18</f>
-        <v>13074269.9424313</v>
+        <v>13160344.1733262</v>
       </c>
       <c r="G20" s="49" t="n">
         <f aca="false">G17-G18</f>
-        <v>17772418.0067083</v>
+        <v>17858492.2376032</v>
       </c>
       <c r="H20" s="49" t="n">
         <f aca="false">H17-H18</f>
-        <v>18494411.5249977</v>
+        <v>18580485.7558926</v>
       </c>
       <c r="I20" s="49" t="n">
         <f aca="false">I17-I18</f>
-        <v>19157793.4754352</v>
+        <v>19243867.7063301</v>
       </c>
       <c r="J20" s="49" t="n">
         <f aca="false">J17-J18</f>
-        <v>19834701.010218</v>
+        <v>19920775.2411128</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="14" t="n">
         <f aca="false">Taxes!D29</f>
-        <v>9625.47122569664</v>
+        <v>0</v>
       </c>
       <c r="E21" s="14" t="n">
         <f aca="false">Taxes!E29</f>
-        <v>1099291.04294347</v>
+        <v>931388.412948486</v>
       </c>
       <c r="F21" s="14" t="n">
         <f aca="false">Taxes!F29</f>
-        <v>1961140.4913647</v>
+        <v>1974051.62599893</v>
       </c>
       <c r="G21" s="14" t="n">
         <f aca="false">Taxes!G29</f>
-        <v>2665862.70100625</v>
+        <v>2678773.83564048</v>
       </c>
       <c r="H21" s="14" t="n">
         <f aca="false">Taxes!H29</f>
-        <v>2774161.72874966</v>
+        <v>2787072.86338389</v>
       </c>
       <c r="I21" s="14" t="n">
         <f aca="false">Taxes!I29</f>
-        <v>2873669.02131528</v>
+        <v>2886580.15594952</v>
       </c>
       <c r="J21" s="14" t="n">
         <f aca="false">Taxes!J29</f>
-        <v>2975205.15153269</v>
+        <v>2988116.28616693</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="39" t="s">
-        <v>475</v>
-      </c>
-      <c r="C22" s="63" t="s">
+        <v>473</v>
+      </c>
+      <c r="C22" s="62" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="17" t="n">
         <f aca="false">D20-D21</f>
-        <v>54544.3369456143</v>
+        <v>-1205425.09752808</v>
       </c>
       <c r="E22" s="17" t="n">
         <f aca="false">E20-E21</f>
-        <v>6229315.91001298</v>
+        <v>6483292.77090284</v>
       </c>
       <c r="F22" s="17" t="n">
         <f aca="false">F20-F21</f>
-        <v>11113129.4510666</v>
+        <v>11186292.5473273</v>
       </c>
       <c r="G22" s="17" t="n">
         <f aca="false">G20-G21</f>
-        <v>15106555.3057021</v>
+        <v>15179718.4019627</v>
       </c>
       <c r="H22" s="17" t="n">
         <f aca="false">H20-H21</f>
-        <v>15720249.7962481</v>
+        <v>15793412.8925087</v>
       </c>
       <c r="I22" s="17" t="n">
         <f aca="false">I20-I21</f>
-        <v>16284124.4541199</v>
+        <v>16357287.5503806</v>
       </c>
       <c r="J22" s="17" t="n">
         <f aca="false">J20-J21</f>
-        <v>16859495.8586853</v>
+        <v>16932658.9549459</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="34" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D25" s="15" t="n">
         <f aca="false">IFERROR(D14/D10,0)</f>
-        <v>0.560280115500751</v>
+        <v>0.562655695457213</v>
       </c>
       <c r="E25" s="15" t="n">
         <f aca="false">IFERROR(E14/E10,0)</f>
-        <v>0.381466526679509</v>
+        <v>0.383806902655317</v>
       </c>
       <c r="F25" s="15" t="n">
         <f aca="false">IFERROR(F14/F10,0)</f>
-        <v>0.410807860486824</v>
+        <v>0.412570747861049</v>
       </c>
       <c r="G25" s="15" t="n">
         <f aca="false">IFERROR(G14/G10,0)</f>
-        <v>0.423640298784274</v>
+        <v>0.425101231965885</v>
       </c>
       <c r="H25" s="15" t="n">
         <f aca="false">IFERROR(H14/H10,0)</f>
-        <v>0.422154469895093</v>
+        <v>0.423575007772194</v>
       </c>
       <c r="I25" s="15" t="n">
         <f aca="false">IFERROR(I14/I10,0)</f>
-        <v>0.422162014111407</v>
+        <v>0.423551982242665</v>
       </c>
       <c r="J25" s="15" t="n">
         <f aca="false">IFERROR(J14/J10,0)</f>
-        <v>0.42219206434207</v>
+        <v>0.423552111181539</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D26" s="15" t="n">
         <f aca="false">IFERROR(D22/D10,0)</f>
-        <v>0.00602152036628819</v>
+        <v>-0.133075075823869</v>
       </c>
       <c r="E26" s="15" t="n">
         <f aca="false">IFERROR(E22/E10,0)</f>
-        <v>0.169376376064544</v>
+        <v>0.176282058955442</v>
       </c>
       <c r="F26" s="15" t="n">
         <f aca="false">IFERROR(F22/F10,0)</f>
-        <v>0.227608140017391</v>
+        <v>0.229106594285482</v>
       </c>
       <c r="G26" s="15" t="n">
         <f aca="false">IFERROR(G22/G10,0)</f>
-        <v>0.256402731415626</v>
+        <v>0.257644524619995</v>
       </c>
       <c r="H26" s="15" t="n">
         <f aca="false">IFERROR(H22/H10,0)</f>
-        <v>0.259441298991447</v>
+        <v>0.260648756186983</v>
       </c>
       <c r="I26" s="15" t="n">
         <f aca="false">IFERROR(I22/I10,0)</f>
-        <v>0.262963883631102</v>
+        <v>0.264145356542672</v>
       </c>
       <c r="J26" s="15" t="n">
         <f aca="false">IFERROR(J22/J10,0)</f>
-        <v>0.266394527366159</v>
+        <v>0.267550567179708</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10829,44 +10824,44 @@
         <v>34</v>
       </c>
       <c r="D27" s="14" t="n">
-        <f aca="false">D17+Depreciate!$G$18</f>
-        <v>731448.935790863</v>
+        <f aca="false">D17+Depreciate!$G$17</f>
+        <v>731448.935790864</v>
       </c>
       <c r="E27" s="14" t="n">
-        <f aca="false">E17+Depreciate!$H$18</f>
+        <f aca="false">E17+Depreciate!$H$17</f>
         <v>11251688.101859</v>
       </c>
       <c r="F27" s="14" t="n">
-        <f aca="false">F17+Depreciate!$I$18</f>
+        <f aca="false">F17+Depreciate!$I$17</f>
         <v>16832637.1521353</v>
       </c>
       <c r="G27" s="14" t="n">
-        <f aca="false">G17+Depreciate!$J$18</f>
+        <f aca="false">G17+Depreciate!$J$17</f>
         <v>21369559.4452465</v>
       </c>
       <c r="H27" s="14" t="n">
-        <f aca="false">H17+Depreciate!$K$18</f>
+        <f aca="false">H17+Depreciate!$K$17</f>
         <v>21930327.1923702</v>
       </c>
       <c r="I27" s="14" t="n">
-        <f aca="false">I17+Depreciate!$L$18</f>
+        <f aca="false">I17+Depreciate!$L$17</f>
         <v>22433613.341568</v>
       </c>
       <c r="J27" s="14" t="n">
-        <f aca="false">J17+Depreciate!$M$18</f>
+        <f aca="false">J17+Depreciate!$M$17</f>
         <v>22948165.1352589</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D28" s="15" t="n">
         <f aca="false">IFERROR(D27/D10,0)</f>
-        <v>0.0807496233413953</v>
+        <v>0.0807496233413954</v>
       </c>
       <c r="E28" s="15" t="n">
         <f aca="false">IFERROR(E27/E10,0)</f>
@@ -10895,38 +10890,38 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="D29" s="21" t="str">
+      <c r="D29" s="21" t="n">
         <f aca="false">IF(D19&gt;0,D17/D19,"-")</f>
-        <v>-</v>
+        <v>0.0663678044746324</v>
       </c>
       <c r="E29" s="21" t="n">
         <f aca="false">IF(E19&gt;0,E17/E19,"-")</f>
-        <v>7.13011860917119</v>
+        <v>7.20211663662249</v>
       </c>
       <c r="F29" s="21" t="n">
         <f aca="false">IF(F19&gt;0,F17/F19,"-")</f>
-        <v>14.3843253809179</v>
+        <v>14.4724408564498</v>
       </c>
       <c r="G29" s="21" t="n">
         <f aca="false">IF(G19&gt;0,G17/G19,"-")</f>
-        <v>24.3341359194246</v>
+        <v>24.4471463045113</v>
       </c>
       <c r="H29" s="21" t="n">
         <f aca="false">IF(H19&gt;0,H17/H19,"-")</f>
-        <v>34.84383202077</v>
+        <v>35.0013434835049</v>
       </c>
       <c r="I29" s="21" t="n">
         <f aca="false">IF(I19&gt;0,I17/I19,"-")</f>
-        <v>58.633427048432</v>
+        <v>58.8923688160938</v>
       </c>
       <c r="J29" s="21" t="n">
         <f aca="false">IF(J19&gt;0,J17/J19,"-")</f>
-        <v>171.853109641877</v>
+        <v>172.594540026981</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10967,14 +10962,14 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C31" s="20" t="s">
         <v>61</v>
       </c>
       <c r="D31" s="21" t="n">
         <f aca="false">IFERROR(D30/D27,0)</f>
-        <v>24.8709282027603</v>
+        <v>24.8709282027602</v>
       </c>
       <c r="E31" s="21" t="n">
         <f aca="false">IFERROR(E30/E27,0)</f>
@@ -11003,7 +10998,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>
@@ -11044,90 +11039,90 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="13" t="s">
-        <v>487</v>
-      </c>
-      <c r="C5" s="59" t="n">
+        <v>485</v>
+      </c>
+      <c r="C5" s="72" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="13" t="s">
-        <v>488</v>
-      </c>
-      <c r="C6" s="59" t="n">
+        <v>486</v>
+      </c>
+      <c r="C6" s="72" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>489</v>
-      </c>
-      <c r="C7" s="59" t="n">
+        <v>487</v>
+      </c>
+      <c r="C7" s="72" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="13" t="s">
-        <v>490</v>
-      </c>
-      <c r="C8" s="59" t="n">
+        <v>488</v>
+      </c>
+      <c r="C8" s="72" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>491</v>
-      </c>
-      <c r="C9" s="59" t="n">
+        <v>489</v>
+      </c>
+      <c r="C9" s="72" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>492</v>
-      </c>
-      <c r="C10" s="59" t="n">
+        <v>490</v>
+      </c>
+      <c r="C10" s="72" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>493</v>
-      </c>
-      <c r="C11" s="59" t="n">
+        <v>491</v>
+      </c>
+      <c r="C11" s="72" t="n">
         <v>90</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>494</v>
-      </c>
-      <c r="C12" s="59" t="n">
+        <v>492</v>
+      </c>
+      <c r="C12" s="72" t="n">
         <v>540</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="19" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>46</v>
@@ -11164,7 +11159,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>0</v>
@@ -11193,7 +11188,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="C17" s="14" t="n">
         <v>0</v>
@@ -11222,7 +11217,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="13" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C18" s="14" t="n">
         <v>0</v>
@@ -11251,7 +11246,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="11" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C19" s="49" t="n">
         <v>0</v>
@@ -11287,7 +11282,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="13" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C20" s="14" t="n">
         <v>0</v>
@@ -11316,7 +11311,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="13" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C21" s="14" t="n">
         <v>0</v>
@@ -11345,7 +11340,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C22" s="49" t="n">
         <v>0</v>
@@ -11381,7 +11376,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="16" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C23" s="17" t="n">
         <v>0</v>
@@ -11417,7 +11412,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="26" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C25" s="22"/>
       <c r="D25" s="22" t="n">
@@ -11451,7 +11446,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14" t="n">
@@ -11478,7 +11473,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="11" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C27" s="49"/>
       <c r="D27" s="49" t="n">
@@ -11512,7 +11507,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -11553,15 +11548,15 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="53" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11606,7 +11601,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>34</v>
@@ -11642,7 +11637,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>34</v>
@@ -11678,7 +11673,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="29" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>34</v>
@@ -11714,7 +11709,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>34</v>
@@ -11749,10 +11744,10 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="72" t="s">
-        <v>513</v>
-      </c>
-      <c r="C10" s="60" t="s">
+      <c r="B10" s="71" t="s">
+        <v>511</v>
+      </c>
+      <c r="C10" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D10" s="49" t="n">
@@ -11786,79 +11781,79 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D11" s="14" t="n">
         <f aca="false">-ProfLoss!D11</f>
-        <v>-3983085.34769568</v>
+        <v>-3961566.78997196</v>
       </c>
       <c r="E11" s="14" t="n">
         <f aca="false">-ProfLoss!E11</f>
-        <v>-22748393.2278882</v>
+        <v>-22662318.9969933</v>
       </c>
       <c r="F11" s="14" t="n">
         <f aca="false">-ProfLoss!F11</f>
-        <v>-28767725.6070918</v>
+        <v>-28681651.3761969</v>
       </c>
       <c r="G11" s="14" t="n">
         <f aca="false">-ProfLoss!G11</f>
-        <v>-33957554.4079507</v>
+        <v>-33871480.1770559</v>
       </c>
       <c r="H11" s="14" t="n">
         <f aca="false">-ProfLoss!H11</f>
-        <v>-35013223.0766929</v>
+        <v>-34927148.845798</v>
       </c>
       <c r="I11" s="14" t="n">
         <f aca="false">-ProfLoss!I11</f>
-        <v>-35782806.1656104</v>
+        <v>-35696731.9347155</v>
       </c>
       <c r="J11" s="14" t="n">
         <f aca="false">-ProfLoss!J11</f>
-        <v>-36568132.9667505</v>
+        <v>-36482058.7358556</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="72" t="s">
-        <v>514</v>
-      </c>
-      <c r="C12" s="60" t="s">
+      <c r="B12" s="71" t="s">
+        <v>512</v>
+      </c>
+      <c r="C12" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="49" t="n">
         <f aca="false">D10+D11</f>
-        <v>-7309339.21964482</v>
+        <v>-7287820.6619211</v>
       </c>
       <c r="E12" s="49" t="n">
         <f aca="false">E10+E11</f>
-        <v>20743099.7316485</v>
+        <v>20829173.9625434</v>
       </c>
       <c r="F12" s="49" t="n">
         <f aca="false">F10+F11</f>
-        <v>18206750.191155</v>
+        <v>18292824.4220499</v>
       </c>
       <c r="G12" s="49" t="n">
         <f aca="false">G10+G11</f>
-        <v>23437793.8961224</v>
+        <v>23523868.1270173</v>
       </c>
       <c r="H12" s="49" t="n">
         <f aca="false">H10+H11</f>
-        <v>25349619.2838122</v>
+        <v>25435693.5147071</v>
       </c>
       <c r="I12" s="49" t="n">
         <f aca="false">I10+I11</f>
-        <v>25938878.4639673</v>
+        <v>26024952.6948622</v>
       </c>
       <c r="J12" s="49" t="n">
         <f aca="false">J10+J11</f>
-        <v>26511405.416814</v>
+        <v>26597479.6477089</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>34</v>
@@ -11894,7 +11889,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>34</v>
@@ -11930,7 +11925,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>34</v>
@@ -11960,115 +11955,115 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D16" s="14" t="n">
         <f aca="false">-ProfLoss!D21</f>
-        <v>-9625.47122569664</v>
+        <v>-0</v>
       </c>
       <c r="E16" s="14" t="n">
         <f aca="false">-ProfLoss!E21</f>
-        <v>-1099291.04294347</v>
+        <v>-931388.412948486</v>
       </c>
       <c r="F16" s="14" t="n">
         <f aca="false">-ProfLoss!F21</f>
-        <v>-1961140.4913647</v>
+        <v>-1974051.62599893</v>
       </c>
       <c r="G16" s="14" t="n">
         <f aca="false">-ProfLoss!G21</f>
-        <v>-2665862.70100625</v>
+        <v>-2678773.83564048</v>
       </c>
       <c r="H16" s="14" t="n">
         <f aca="false">-ProfLoss!H21</f>
-        <v>-2774161.72874966</v>
+        <v>-2787072.86338389</v>
       </c>
       <c r="I16" s="14" t="n">
         <f aca="false">-ProfLoss!I21</f>
-        <v>-2873669.02131528</v>
+        <v>-2886580.15594952</v>
       </c>
       <c r="J16" s="14" t="n">
         <f aca="false">-ProfLoss!J21</f>
-        <v>-2975205.15153269</v>
+        <v>-2988116.28616693</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D17" s="14" t="n">
-        <f aca="false">Depreciate!$G$18</f>
-        <v>667279.127619552</v>
+        <f aca="false">Depreciate!$G$17</f>
+        <v>645760.569895833</v>
       </c>
       <c r="E17" s="14" t="n">
-        <f aca="false">Depreciate!$H$18</f>
-        <v>2727572.96705559</v>
+        <f aca="false">Depreciate!$H$17</f>
+        <v>2641498.73616072</v>
       </c>
       <c r="F17" s="14" t="n">
-        <f aca="false">Depreciate!$I$18</f>
-        <v>2781532.77312702</v>
+        <f aca="false">Depreciate!$I$17</f>
+        <v>2695458.54223215</v>
       </c>
       <c r="G17" s="14" t="n">
-        <f aca="false">Depreciate!$J$18</f>
-        <v>2835492.57919845</v>
+        <f aca="false">Depreciate!$J$17</f>
+        <v>2749418.34830358</v>
       </c>
       <c r="H17" s="14" t="n">
-        <f aca="false">Depreciate!$K$18</f>
-        <v>2889452.38526988</v>
+        <f aca="false">Depreciate!$K$17</f>
+        <v>2803378.154375</v>
       </c>
       <c r="I17" s="14" t="n">
-        <f aca="false">Depreciate!$L$18</f>
-        <v>2943412.19134131</v>
+        <f aca="false">Depreciate!$L$17</f>
+        <v>2857337.96044643</v>
       </c>
       <c r="J17" s="14" t="n">
-        <f aca="false">Depreciate!$M$18</f>
-        <v>2997371.99741274</v>
+        <f aca="false">Depreciate!$M$17</f>
+        <v>2911297.76651786</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="62" t="s">
         <v>34</v>
       </c>
       <c r="D18" s="17" t="n">
         <f aca="false">SUM(D12:D17)</f>
-        <v>-12856917.8800911</v>
+        <v>-12847292.4088654</v>
       </c>
       <c r="E18" s="17" t="n">
         <f aca="false">SUM(E12:E17)</f>
-        <v>16865939.9007855</v>
+        <v>17033842.5307805</v>
       </c>
       <c r="F18" s="17" t="n">
         <f aca="false">SUM(F12:F17)</f>
-        <v>13020260.6447673</v>
+        <v>13007349.510133</v>
       </c>
       <c r="G18" s="17" t="n">
         <f aca="false">SUM(G12:G17)</f>
-        <v>17181750.2820009</v>
+        <v>17168839.1473667</v>
       </c>
       <c r="H18" s="17" t="n">
         <f aca="false">SUM(H12:H17)</f>
-        <v>18926303.9741256</v>
+        <v>18913392.8394914</v>
       </c>
       <c r="I18" s="17" t="n">
         <f aca="false">SUM(I12:I17)</f>
-        <v>19356302.0598304</v>
+        <v>19343390.9251962</v>
       </c>
       <c r="J18" s="17" t="n">
         <f aca="false">SUM(J12:J17)</f>
-        <v>19764802.3872907</v>
+        <v>19751891.2526565</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C19" s="20" t="s">
         <v>34</v>
@@ -12098,7 +12093,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="7" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C20" s="20" t="s">
         <v>34</v>
@@ -12134,50 +12129,50 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C21" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D21" s="14" t="n">
-        <f aca="false">-Depreciate!$G$22</f>
+        <f aca="false">-Depreciate!$G$21</f>
         <v>-54094705.5866071</v>
       </c>
       <c r="E21" s="14" t="n">
-        <f aca="false">-Depreciate!$H$22</f>
+        <f aca="false">-Depreciate!$H$21</f>
         <v>-539598.060714286</v>
       </c>
       <c r="F21" s="14" t="n">
-        <f aca="false">-Depreciate!$I$22</f>
+        <f aca="false">-Depreciate!$I$21</f>
         <v>-539598.060714286</v>
       </c>
       <c r="G21" s="14" t="n">
-        <f aca="false">-Depreciate!$J$22</f>
+        <f aca="false">-Depreciate!$J$21</f>
         <v>-539598.060714286</v>
       </c>
       <c r="H21" s="14" t="n">
-        <f aca="false">-Depreciate!$K$22</f>
+        <f aca="false">-Depreciate!$K$21</f>
         <v>-539598.060714286</v>
       </c>
       <c r="I21" s="14" t="n">
-        <f aca="false">-Depreciate!$L$22</f>
+        <f aca="false">-Depreciate!$L$21</f>
         <v>-539598.060714286</v>
       </c>
       <c r="J21" s="14" t="n">
-        <f aca="false">-Depreciate!$M$22</f>
+        <f aca="false">-Depreciate!$M$21</f>
         <v>-539598.060714286</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C22" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="14" t="n">
         <f aca="false">-ProfLoss!D19</f>
-        <v>-0</v>
+        <v>-1291113.46342311</v>
       </c>
       <c r="E22" s="14" t="n">
         <f aca="false">-ProfLoss!E19</f>
@@ -12206,14 +12201,13 @@
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D23" s="14" t="n">
-        <f aca="false">-LOANS!$C$106</f>
-        <v>-1291113.46342311</v>
+        <v>0</v>
       </c>
       <c r="E23" s="14" t="n">
         <v>0</v>
@@ -12235,44 +12229,44 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="72" t="s">
-        <v>523</v>
-      </c>
-      <c r="C24" s="60" t="s">
+      <c r="B24" s="71" t="s">
+        <v>521</v>
+      </c>
+      <c r="C24" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D24" s="49" t="n">
         <f aca="false">D18+D19+D20+D21+D22+D23</f>
-        <v>903741.604225626</v>
+        <v>913367.075451335</v>
       </c>
       <c r="E24" s="49" t="n">
         <f aca="false">E18+E19+E20+E21+E22+E23</f>
-        <v>15130833.6582242</v>
+        <v>15298736.2882192</v>
       </c>
       <c r="F24" s="49" t="n">
         <f aca="false">F18+F19+F20+F21+F22+F23</f>
-        <v>11503828.147476</v>
+        <v>11490917.0128418</v>
       </c>
       <c r="G24" s="49" t="n">
         <f aca="false">G18+G19+G20+G21+G22+G23</f>
-        <v>15880503.3619469</v>
+        <v>15867592.2273127</v>
       </c>
       <c r="H24" s="49" t="n">
         <f aca="false">H18+H19+H20+H21+H22+H23</f>
-        <v>17840242.6313088</v>
+        <v>17827331.4966745</v>
       </c>
       <c r="I24" s="49" t="n">
         <f aca="false">I18+I19+I20+I21+I22+I23</f>
-        <v>18484296.3243247</v>
+        <v>18471385.1896904</v>
       </c>
       <c r="J24" s="49" t="n">
         <f aca="false">J18+J19+J20+J21+J22+J23</f>
-        <v>19109112.1989483</v>
+        <v>19096201.064314</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>34</v>
@@ -12310,36 +12304,36 @@
       <c r="B26" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="63" t="s">
+      <c r="C26" s="62" t="s">
         <v>34</v>
       </c>
       <c r="D26" s="17" t="n">
         <f aca="false">D24+D25</f>
-        <v>903741.604225626</v>
+        <v>913367.075451335</v>
       </c>
       <c r="E26" s="17" t="n">
         <f aca="false">E24+E25</f>
-        <v>12098864.6638843</v>
+        <v>12266767.2938792</v>
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">F24+F25</f>
-        <v>8471859.15313605</v>
+        <v>8458948.01850181</v>
       </c>
       <c r="G26" s="17" t="n">
         <f aca="false">G24+G25</f>
-        <v>12848534.3676069</v>
+        <v>12835623.2329727</v>
       </c>
       <c r="H26" s="17" t="n">
         <f aca="false">H24+H25</f>
-        <v>14808273.6369688</v>
+        <v>14795362.5023346</v>
       </c>
       <c r="I26" s="17" t="n">
         <f aca="false">I24+I25</f>
-        <v>15452327.3299847</v>
+        <v>15439416.1953504</v>
       </c>
       <c r="J26" s="17" t="n">
         <f aca="false">J24+J25</f>
-        <v>16077143.2046083</v>
+        <v>16064232.069974</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12351,36 +12345,36 @@
       </c>
       <c r="D27" s="22" t="n">
         <f aca="false">D26</f>
-        <v>903741.604225626</v>
+        <v>913367.075451335</v>
       </c>
       <c r="E27" s="22" t="n">
         <f aca="false">D27+E26</f>
-        <v>13002606.2681099</v>
+        <v>13180134.3693306</v>
       </c>
       <c r="F27" s="22" t="n">
         <f aca="false">E27+F26</f>
-        <v>21474465.4212459</v>
+        <v>21639082.3878324</v>
       </c>
       <c r="G27" s="22" t="n">
         <f aca="false">F27+G26</f>
-        <v>34322999.7888528</v>
+        <v>34474705.6208051</v>
       </c>
       <c r="H27" s="22" t="n">
         <f aca="false">G27+H26</f>
-        <v>49131273.4258216</v>
+        <v>49270068.1231396</v>
       </c>
       <c r="I27" s="22" t="n">
         <f aca="false">H27+I26</f>
-        <v>64583600.7558063</v>
+        <v>64709484.31849</v>
       </c>
       <c r="J27" s="22" t="n">
         <f aca="false">I27+J26</f>
-        <v>80660743.9604145</v>
+        <v>80773716.3884641</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C29" s="20" t="s">
         <v>61</v>
@@ -12391,32 +12385,32 @@
       </c>
       <c r="E29" s="21" t="n">
         <f aca="false">IFERROR(E18/-(E22+E25),0)</f>
-        <v>3.9895992805804</v>
+        <v>4.02931626141728</v>
       </c>
       <c r="F29" s="21" t="n">
         <f aca="false">IFERROR(F18/-(F22+F25),0)</f>
-        <v>3.24791695805079</v>
+        <v>3.24469626268452</v>
       </c>
       <c r="G29" s="21" t="n">
         <f aca="false">IFERROR(G18/-(G22+G25),0)</f>
-        <v>4.52911994425979</v>
+        <v>4.5257165612275</v>
       </c>
       <c r="H29" s="21" t="n">
         <f aca="false">IFERROR(H18/-(H22+H25),0)</f>
-        <v>5.28899319926237</v>
+        <v>5.28538515707048</v>
       </c>
       <c r="I29" s="21" t="n">
         <f aca="false">IFERROR(I18/-(I22+I25),0)</f>
-        <v>5.75331003731732</v>
+        <v>5.74947243650624</v>
       </c>
       <c r="J29" s="21" t="n">
         <f aca="false">IFERROR(J18/-(J22+J25),0)</f>
-        <v>6.27840490432845</v>
+        <v>6.27430360701114</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="7" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C30" s="20" t="s">
         <v>61</v>
@@ -12427,50 +12421,50 @@
       </c>
       <c r="E30" s="21" t="n">
         <f aca="false">IFERROR((E18+E21)/-(E22+E25),0)</f>
-        <v>3.86195860075513</v>
+        <v>3.90167558159202</v>
       </c>
       <c r="F30" s="21" t="n">
         <f aca="false">IFERROR((F18+F21)/-(F22+F25),0)</f>
-        <v>3.11331368552493</v>
+        <v>3.11009299015867</v>
       </c>
       <c r="G30" s="21" t="n">
         <f aca="false">IFERROR((G18+G21)/-(G22+G25),0)</f>
-        <v>4.38688156350384</v>
+        <v>4.38347818047154</v>
       </c>
       <c r="H30" s="21" t="n">
         <f aca="false">IFERROR((H18+H21)/-(H22+H25),0)</f>
-        <v>5.13820145052185</v>
+        <v>5.13459340832996</v>
       </c>
       <c r="I30" s="21" t="n">
         <f aca="false">IFERROR((I18+I21)/-(I22+I25),0)</f>
-        <v>5.59292429167083</v>
+        <v>5.58908669085975</v>
       </c>
       <c r="J30" s="21" t="n">
         <f aca="false">IFERROR((J18+J21)/-(J22+J25),0)</f>
-        <v>6.1069984291019</v>
+        <v>6.1028971317846</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="26" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D31" s="77" t="n">
         <f aca="false">MIN(E30:J30)</f>
-        <v>3.11331368552493</v>
+        <v>3.11009299015867</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="26" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D32" s="77" t="n">
         <f aca="false">AVERAGE(E30:J30)</f>
-        <v>4.70004633684642</v>
+        <v>4.70363733053276</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>
@@ -12511,20 +12505,20 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="D2" s="52" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="53" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="26" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C4" s="22" t="n">
         <f aca="false">CostTotal!C26</f>
@@ -12551,16 +12545,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C7" s="14" t="n">
         <f aca="false">CostTotal!F22</f>
-        <v>9798442.05271821</v>
+        <v>9712367.82182333</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C8" s="14" t="n">
         <f aca="false">CostTotal!G22</f>
@@ -12569,7 +12563,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C9" s="14" t="n">
         <f aca="false">C4-C8</f>
@@ -12578,41 +12572,41 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="26" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C10" s="23" t="n">
         <f aca="false">IFERROR(C7/C9,0)</f>
-        <v>0.350149080497285</v>
+        <v>0.34707320245053</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C11" s="14" t="n">
         <f aca="false">C10*C4</f>
-        <v>20629836.5878118</v>
+        <v>20448614.174266</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>537</v>
-      </c>
-      <c r="C12" s="62" t="n">
+        <v>535</v>
+      </c>
+      <c r="C12" s="61" t="n">
         <f aca="false">C10*ProdPlan!G17</f>
-        <v>694.370137061751</v>
+        <v>688.270455583574</v>
       </c>
       <c r="D12" s="73" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C13" s="15" t="n">
         <f aca="false">1-C10</f>
-        <v>0.649850919502715</v>
+        <v>0.65292679754947</v>
       </c>
     </row>
   </sheetData>
@@ -12642,12 +12636,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="53" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12692,28 +12686,28 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="7" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C6" s="20"/>
-      <c r="D6" s="59" t="n">
+      <c r="D6" s="72" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="59" t="n">
+      <c r="E6" s="72" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="59" t="n">
+      <c r="F6" s="72" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="59" t="n">
+      <c r="G6" s="72" t="n">
         <v>4</v>
       </c>
-      <c r="H6" s="59" t="n">
+      <c r="H6" s="72" t="n">
         <v>5</v>
       </c>
-      <c r="I6" s="59" t="n">
+      <c r="I6" s="72" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="59" t="n">
+      <c r="J6" s="72" t="n">
         <v>7</v>
       </c>
     </row>
@@ -12726,36 +12720,36 @@
       </c>
       <c r="D7" s="14" t="n">
         <f aca="false">CashFlow!D18</f>
-        <v>-12856917.8800911</v>
+        <v>-12847292.4088654</v>
       </c>
       <c r="E7" s="14" t="n">
         <f aca="false">CashFlow!E18</f>
-        <v>16865939.9007855</v>
+        <v>17033842.5307805</v>
       </c>
       <c r="F7" s="14" t="n">
         <f aca="false">CashFlow!F18</f>
-        <v>13020260.6447673</v>
+        <v>13007349.510133</v>
       </c>
       <c r="G7" s="14" t="n">
         <f aca="false">CashFlow!G18</f>
-        <v>17181750.2820009</v>
+        <v>17168839.1473667</v>
       </c>
       <c r="H7" s="14" t="n">
         <f aca="false">CashFlow!H18</f>
-        <v>18926303.9741256</v>
+        <v>18913392.8394914</v>
       </c>
       <c r="I7" s="14" t="n">
         <f aca="false">CashFlow!I18</f>
-        <v>19356302.0598304</v>
+        <v>19343390.9251962</v>
       </c>
       <c r="J7" s="14" t="n">
         <f aca="false">CashFlow!J18</f>
-        <v>19764802.3872907</v>
+        <v>19751891.2526565</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>34</v>
@@ -12790,47 +12784,47 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="72" t="s">
-        <v>543</v>
-      </c>
-      <c r="C9" s="60" t="s">
+      <c r="B9" s="71" t="s">
+        <v>541</v>
+      </c>
+      <c r="C9" s="59" t="s">
         <v>34</v>
       </c>
       <c r="D9" s="49" t="n">
         <f aca="false">D7+D8</f>
-        <v>-66951623.4666982</v>
+        <v>-66941997.9954725</v>
       </c>
       <c r="E9" s="49" t="n">
         <f aca="false">E7+E8</f>
-        <v>16326341.8400712</v>
+        <v>16494244.4700662</v>
       </c>
       <c r="F9" s="49" t="n">
         <f aca="false">F7+F8</f>
-        <v>12480662.584053</v>
+        <v>12467751.4494187</v>
       </c>
       <c r="G9" s="49" t="n">
         <f aca="false">G7+G8</f>
-        <v>16642152.2212866</v>
+        <v>16629241.0866524</v>
       </c>
       <c r="H9" s="49" t="n">
         <f aca="false">H7+H8</f>
-        <v>18386705.9134113</v>
+        <v>18373794.7787771</v>
       </c>
       <c r="I9" s="49" t="n">
         <f aca="false">I7+I8</f>
-        <v>18816703.9991162</v>
+        <v>18803792.8644819</v>
       </c>
       <c r="J9" s="49" t="n">
         <f aca="false">J7+J8</f>
-        <v>19225204.3265765</v>
+        <v>19212293.1919422</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="7" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D10" s="15" t="n">
         <v>0.111708147552152</v>
@@ -12862,7 +12856,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C11" s="20"/>
       <c r="D11" s="78" t="n">
@@ -12896,115 +12890,115 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="C12" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="14" t="n">
         <f aca="false">D9*D11</f>
-        <v>-60224100.7355372</v>
+        <v>-60215442.4638074</v>
       </c>
       <c r="E12" s="14" t="n">
         <f aca="false">E9*E11</f>
-        <v>13210136.5970495</v>
+        <v>13345991.689327</v>
       </c>
       <c r="F12" s="14" t="n">
         <f aca="false">F9*F11</f>
-        <v>9083752.1603395</v>
+        <v>9074355.0993793</v>
       </c>
       <c r="G12" s="14" t="n">
         <f aca="false">G9*G11</f>
-        <v>10895479.1974955</v>
+        <v>10887026.3846049</v>
       </c>
       <c r="H12" s="14" t="n">
         <f aca="false">H9*H11</f>
-        <v>10828043.3803977</v>
+        <v>10820439.9343771</v>
       </c>
       <c r="I12" s="14" t="n">
         <f aca="false">I9*I11</f>
-        <v>9967788.67098198</v>
+        <v>9960949.24461153</v>
       </c>
       <c r="J12" s="14" t="n">
         <f aca="false">J9*J11</f>
-        <v>9160843.08688291</v>
+        <v>9154690.90891649</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D13" s="14" t="n">
         <f aca="false">D9</f>
-        <v>-66951623.4666982</v>
+        <v>-66941997.9954725</v>
       </c>
       <c r="E13" s="14" t="n">
         <f aca="false">D13+E9</f>
-        <v>-50625281.626627</v>
+        <v>-50447753.5254063</v>
       </c>
       <c r="F13" s="14" t="n">
         <f aca="false">E13+F9</f>
-        <v>-38144619.0425741</v>
+        <v>-37980002.0759876</v>
       </c>
       <c r="G13" s="14" t="n">
         <f aca="false">F13+G9</f>
-        <v>-21502466.8212874</v>
+        <v>-21350760.9893352</v>
       </c>
       <c r="H13" s="14" t="n">
         <f aca="false">G13+H9</f>
-        <v>-3115760.90787609</v>
+        <v>-2976966.2105581</v>
       </c>
       <c r="I13" s="14" t="n">
         <f aca="false">H13+I9</f>
-        <v>15700943.0912401</v>
+        <v>15826826.6539238</v>
       </c>
       <c r="J13" s="14" t="n">
         <f aca="false">I13+J9</f>
-        <v>34926147.4178165</v>
+        <v>35039119.8458661</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>34</v>
       </c>
       <c r="D14" s="14" t="n">
         <f aca="false">D12</f>
-        <v>-60224100.7355372</v>
+        <v>-60215442.4638074</v>
       </c>
       <c r="E14" s="14" t="n">
         <f aca="false">D14+E12</f>
-        <v>-47013964.1384877</v>
+        <v>-46869450.7744804</v>
       </c>
       <c r="F14" s="14" t="n">
         <f aca="false">E14+F12</f>
-        <v>-37930211.9781482</v>
+        <v>-37795095.6751011</v>
       </c>
       <c r="G14" s="14" t="n">
         <f aca="false">F14+G12</f>
-        <v>-27034732.7806527</v>
+        <v>-26908069.2904962</v>
       </c>
       <c r="H14" s="14" t="n">
         <f aca="false">G14+H12</f>
-        <v>-16206689.4002549</v>
+        <v>-16087629.356119</v>
       </c>
       <c r="I14" s="14" t="n">
         <f aca="false">H14+I12</f>
-        <v>-6238900.72927294</v>
+        <v>-6126680.1115075</v>
       </c>
       <c r="J14" s="14" t="n">
         <f aca="false">I14+J12</f>
-        <v>2921942.35760997</v>
+        <v>3028010.79740899</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C15" s="20"/>
       <c r="D15" s="79" t="str">
@@ -13029,7 +13023,7 @@
       </c>
       <c r="I15" s="79" t="n">
         <f aca="false">IF(AND(H13&lt;0,I13&gt;=0),H6-H13/I9,"")</f>
-        <v>5.16558483930142</v>
+        <v>5.15831732629757</v>
       </c>
       <c r="J15" s="79" t="str">
         <f aca="false">IF(AND(I13&lt;0,J13&gt;=0),I6-I13/J9,"")</f>
@@ -13038,7 +13032,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C16" s="20"/>
       <c r="D16" s="79" t="str">
@@ -13067,27 +13061,27 @@
       </c>
       <c r="J16" s="79" t="n">
         <f aca="false">IF(AND(I14&lt;0,J14&gt;=0),I6-I14/J12,"")</f>
-        <v>6.68104001674324</v>
+        <v>6.66923942844867</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="16" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="17" t="n">
         <f aca="false">SUM(D12:J12)</f>
-        <v>2921942.35760998</v>
+        <v>3028010.79740899</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="16" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="18" t="n">
         <f aca="false">IFERROR(IRR(D9:J9),"-")</f>
-        <v>0.127593983562719</v>
+        <v>0.128193840540597</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13097,17 +13091,17 @@
       <c r="C20" s="16"/>
       <c r="D20" s="80" t="n">
         <f aca="false">IFERROR(SUM(E12:J12)/-D12,0)</f>
-        <v>1.04851782462375</v>
+        <v>1.0502862832774</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="16" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="81" t="n">
         <f aca="false">IF(COUNT(E15:J15)&gt;0,SUM(E15:J15),"&gt; 7")</f>
-        <v>5.16558483930142</v>
+        <v>5.15831732629757</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13117,7 +13111,7 @@
       <c r="C22" s="16"/>
       <c r="D22" s="81" t="n">
         <f aca="false">IF(COUNT(E16:J16)&gt;0,SUM(E16:J16),"&gt; 7")</f>
-        <v>6.68104001674324</v>
+        <v>6.66923942844867</v>
       </c>
     </row>
   </sheetData>
@@ -15053,266 +15047,220 @@
         <v>337248.787946429</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="59" t="s">
         <v>214</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="49" t="n">
+        <f aca="false">SUM(D7:D16)</f>
+        <v>57332293.9508929</v>
+      </c>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="49" t="n">
+        <f aca="false">SUM(G7:G16)</f>
+        <v>645760.569895833</v>
+      </c>
+      <c r="H17" s="49" t="n">
+        <f aca="false">SUM(H7:H16)</f>
+        <v>2641498.73616072</v>
+      </c>
+      <c r="I17" s="49" t="n">
+        <f aca="false">SUM(I7:I16)</f>
+        <v>2695458.54223215</v>
+      </c>
+      <c r="J17" s="49" t="n">
+        <f aca="false">SUM(J7:J16)</f>
+        <v>2749418.34830358</v>
+      </c>
+      <c r="K17" s="49" t="n">
+        <f aca="false">SUM(K7:K16)</f>
+        <v>2803378.154375</v>
+      </c>
+      <c r="L17" s="49" t="n">
+        <f aca="false">SUM(L7:L16)</f>
+        <v>2857337.96044643</v>
+      </c>
+      <c r="M17" s="49" t="n">
+        <f aca="false">SUM(M7:M16)</f>
+        <v>2911297.76651786</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="14" t="n">
-        <f aca="false">LOANS!$C$106</f>
-        <v>1291113.46342311</v>
-      </c>
-      <c r="E17" s="59" t="n">
-        <v>15</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <f aca="false">1/E17</f>
-        <v>0.0666666666666667</v>
-      </c>
-      <c r="G17" s="14" t="n">
-        <f aca="false">D17/E17*3/12</f>
-        <v>21518.5577237185</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <f aca="false">D17/E17</f>
-        <v>86074.2308948742</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <f aca="false">D17/E17</f>
-        <v>86074.2308948742</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <f aca="false">D17/E17</f>
-        <v>86074.2308948742</v>
-      </c>
-      <c r="K17" s="14" t="n">
-        <f aca="false">D17/E17</f>
-        <v>86074.2308948742</v>
-      </c>
-      <c r="L17" s="14" t="n">
-        <f aca="false">D17/E17</f>
-        <v>86074.2308948742</v>
-      </c>
-      <c r="M17" s="14" t="n">
-        <f aca="false">D17/E17</f>
-        <v>86074.2308948742</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="C18" s="60" t="s">
-        <v>216</v>
-      </c>
-      <c r="D18" s="49" t="n">
-        <f aca="false">SUM(D7:D17)</f>
-        <v>58623407.414316</v>
-      </c>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="49" t="n">
-        <f aca="false">SUM(G7:G17)</f>
-        <v>667279.127619552</v>
-      </c>
-      <c r="H18" s="49" t="n">
-        <f aca="false">SUM(H7:H17)</f>
-        <v>2727572.96705559</v>
-      </c>
-      <c r="I18" s="49" t="n">
-        <f aca="false">SUM(I7:I17)</f>
-        <v>2781532.77312702</v>
-      </c>
-      <c r="J18" s="49" t="n">
-        <f aca="false">SUM(J7:J17)</f>
-        <v>2835492.57919845</v>
-      </c>
-      <c r="K18" s="49" t="n">
-        <f aca="false">SUM(K7:K17)</f>
-        <v>2889452.38526988</v>
-      </c>
-      <c r="L18" s="49" t="n">
-        <f aca="false">SUM(L7:L17)</f>
-        <v>2943412.19134131</v>
-      </c>
-      <c r="M18" s="49" t="n">
-        <f aca="false">SUM(M7:M17)</f>
-        <v>2997371.99741274</v>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="14" t="n">
+        <f aca="false">G17-G19</f>
+        <v>544620.483137619</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <f aca="false">H17-H19</f>
+        <v>2236938.38912786</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <f aca="false">I17-I19</f>
+        <v>2290898.19519929</v>
+      </c>
+      <c r="J18" s="14" t="n">
+        <f aca="false">J17-J19</f>
+        <v>2344858.00127072</v>
+      </c>
+      <c r="K18" s="14" t="n">
+        <f aca="false">K17-K19</f>
+        <v>2398817.80734215</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <f aca="false">L17-L19</f>
+        <v>2452777.61341358</v>
+      </c>
+      <c r="M18" s="14" t="n">
+        <f aca="false">M17-M19</f>
+        <v>2506737.419485</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
       <c r="G19" s="14" t="n">
-        <f aca="false">G18-G20</f>
-        <v>566139.040861338</v>
+        <v>101140.086758214</v>
       </c>
       <c r="H19" s="14" t="n">
-        <f aca="false">H18-H20</f>
-        <v>2323012.62002274</v>
+        <v>404560.347032858</v>
       </c>
       <c r="I19" s="14" t="n">
-        <f aca="false">I18-I20</f>
-        <v>2376972.42609416</v>
+        <v>404560.347032858</v>
       </c>
       <c r="J19" s="14" t="n">
-        <f aca="false">J18-J20</f>
-        <v>2430932.23216559</v>
+        <v>404560.347032858</v>
       </c>
       <c r="K19" s="14" t="n">
-        <f aca="false">K18-K20</f>
-        <v>2484892.03823702</v>
+        <v>404560.347032858</v>
       </c>
       <c r="L19" s="14" t="n">
-        <f aca="false">L18-L20</f>
-        <v>2538851.84430845</v>
+        <v>404560.347032858</v>
       </c>
       <c r="M19" s="14" t="n">
-        <f aca="false">M18-M20</f>
-        <v>2592811.65037988</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="7" t="s">
+        <v>404560.347032858</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="14" t="n">
+        <v>54094705.5866071</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>539598.060714286</v>
+      </c>
+      <c r="I21" s="14" t="n">
+        <v>539598.060714286</v>
+      </c>
+      <c r="J21" s="14" t="n">
+        <v>539598.060714286</v>
+      </c>
+      <c r="K21" s="14" t="n">
+        <v>539598.060714286</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>539598.060714286</v>
+      </c>
+      <c r="M21" s="14" t="n">
+        <v>539598.060714286</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="29" t="s">
         <v>218</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="14" t="n">
-        <v>101140.086758214</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <v>404560.347032858</v>
-      </c>
-      <c r="I20" s="14" t="n">
-        <v>404560.347032858</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <v>404560.347032858</v>
-      </c>
-      <c r="K20" s="14" t="n">
-        <v>404560.347032858</v>
-      </c>
-      <c r="L20" s="14" t="n">
-        <v>404560.347032858</v>
-      </c>
-      <c r="M20" s="14" t="n">
-        <v>404560.347032858</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
-        <v>219</v>
       </c>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
       <c r="F22" s="13"/>
       <c r="G22" s="14" t="n">
-        <v>54094705.5866071</v>
+        <f aca="false">SUM($G$17:G17)</f>
+        <v>645760.569895833</v>
       </c>
       <c r="H22" s="14" t="n">
-        <v>539598.060714286</v>
+        <f aca="false">SUM($G$17:H17)</f>
+        <v>3287259.30605655</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>539598.060714286</v>
+        <f aca="false">SUM($G$17:I17)</f>
+        <v>5982717.8482887</v>
       </c>
       <c r="J22" s="14" t="n">
-        <v>539598.060714286</v>
+        <f aca="false">SUM($G$17:J17)</f>
+        <v>8732136.19659228</v>
       </c>
       <c r="K22" s="14" t="n">
-        <v>539598.060714286</v>
+        <f aca="false">SUM($G$17:K17)</f>
+        <v>11535514.3509673</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>539598.060714286</v>
+        <f aca="false">SUM($G$17:L17)</f>
+        <v>14392852.3114137</v>
       </c>
       <c r="M22" s="14" t="n">
-        <v>539598.060714286</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">SUM($G$17:M17)</f>
+        <v>17304150.0779316</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="29" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
       <c r="G23" s="14" t="n">
-        <f aca="false">SUM($G$18:G18)</f>
-        <v>667279.127619552</v>
+        <f aca="false">G21-G17</f>
+        <v>53448945.0167113</v>
       </c>
       <c r="H23" s="14" t="n">
-        <f aca="false">SUM($G$18:H18)</f>
-        <v>3394852.09467515</v>
+        <f aca="false">G23+H21-H17</f>
+        <v>51347044.3412648</v>
       </c>
       <c r="I23" s="14" t="n">
-        <f aca="false">SUM($G$18:I18)</f>
-        <v>6176384.86780217</v>
+        <f aca="false">H23+I21-I17</f>
+        <v>49191183.859747</v>
       </c>
       <c r="J23" s="14" t="n">
-        <f aca="false">SUM($G$18:J18)</f>
-        <v>9011877.44700062</v>
+        <f aca="false">I23+J21-J17</f>
+        <v>46981363.5721577</v>
       </c>
       <c r="K23" s="14" t="n">
-        <f aca="false">SUM($G$18:K18)</f>
-        <v>11901329.8322705</v>
+        <f aca="false">J23+K21-K17</f>
+        <v>44717583.478497</v>
       </c>
       <c r="L23" s="14" t="n">
-        <f aca="false">SUM($G$18:L18)</f>
-        <v>14844742.0236118</v>
+        <f aca="false">K23+L21-L17</f>
+        <v>42399843.5787648</v>
       </c>
       <c r="M23" s="14" t="n">
-        <f aca="false">SUM($G$18:M18)</f>
-        <v>17842114.0210245</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="14" t="n">
-        <f aca="false">G22+$D$17-G18</f>
-        <v>54718539.9224107</v>
-      </c>
-      <c r="H24" s="14" t="n">
-        <f aca="false">G24+H22-H18</f>
-        <v>52530565.0160694</v>
-      </c>
-      <c r="I24" s="14" t="n">
-        <f aca="false">H24+I22-I18</f>
-        <v>50288630.3036566</v>
-      </c>
-      <c r="J24" s="14" t="n">
-        <f aca="false">I24+J22-J18</f>
-        <v>47992735.7851725</v>
-      </c>
-      <c r="K24" s="14" t="n">
-        <f aca="false">J24+K22-K18</f>
-        <v>45642881.4606169</v>
-      </c>
-      <c r="L24" s="14" t="n">
-        <f aca="false">K24+L22-L18</f>
-        <v>43239067.3299899</v>
-      </c>
-      <c r="M24" s="14" t="n">
-        <f aca="false">L24+M22-M18</f>
-        <v>40781293.3932914</v>
-      </c>
-    </row>
+        <f aca="false">L23+M21-M17</f>
+        <v>40028143.8729613</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="B5:B6"/>
@@ -15354,47 +15302,47 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="19" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>45</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="H4" s="19" t="s">
         <v>226</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>227</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" s="61" t="n">
+        <v>1983.07</v>
+      </c>
+      <c r="E5" s="20" t="s">
         <v>229</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D5" s="62" t="n">
-        <v>1983.07</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>231</v>
       </c>
       <c r="F5" s="30" t="n">
         <f aca="false">G32</f>
@@ -15410,16 +15358,16 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D6" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D6" s="61" t="n">
         <v>609.57</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F6" s="30" t="n">
         <f aca="false">G33</f>
@@ -15435,16 +15383,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D7" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D7" s="61" t="n">
         <v>3000</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F7" s="30" t="n">
         <f aca="false">G34</f>
@@ -15517,23 +15465,23 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
+        <v>233</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D13" s="15" t="n">
         <v>0.15</v>
@@ -15559,10 +15507,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D14" s="15" t="n">
         <v>0.15</v>
@@ -15588,10 +15536,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>234</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>236</v>
       </c>
       <c r="D15" s="15" t="n">
         <v>0.15</v>
@@ -15617,452 +15565,452 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
+        <v>235</v>
+      </c>
+      <c r="C16" s="60"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="60"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="60"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D17" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D17" s="61" t="n">
         <f aca="false">$D$5*D13</f>
         <v>297.4605</v>
       </c>
-      <c r="E17" s="62" t="n">
+      <c r="E17" s="61" t="n">
         <f aca="false">$D$5*E13</f>
         <v>1288.9955</v>
       </c>
-      <c r="F17" s="62" t="n">
+      <c r="F17" s="61" t="n">
         <f aca="false">$D$5*F13</f>
         <v>1685.6095</v>
       </c>
-      <c r="G17" s="62" t="n">
+      <c r="G17" s="61" t="n">
         <f aca="false">$D$5*G13</f>
         <v>1983.07</v>
       </c>
-      <c r="H17" s="62" t="n">
+      <c r="H17" s="61" t="n">
         <f aca="false">$D$5*H13</f>
         <v>1983.07</v>
       </c>
-      <c r="I17" s="62" t="n">
+      <c r="I17" s="61" t="n">
         <f aca="false">$D$5*I13</f>
         <v>1983.07</v>
       </c>
-      <c r="J17" s="62" t="n">
+      <c r="J17" s="61" t="n">
         <f aca="false">$D$5*J13</f>
         <v>1983.07</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D18" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D18" s="61" t="n">
         <f aca="false">$D$6*D14</f>
         <v>91.4355</v>
       </c>
-      <c r="E18" s="62" t="n">
+      <c r="E18" s="61" t="n">
         <f aca="false">$D$6*E14</f>
         <v>396.2205</v>
       </c>
-      <c r="F18" s="62" t="n">
+      <c r="F18" s="61" t="n">
         <f aca="false">$D$6*F14</f>
         <v>518.1345</v>
       </c>
-      <c r="G18" s="62" t="n">
+      <c r="G18" s="61" t="n">
         <f aca="false">$D$6*G14</f>
         <v>609.57</v>
       </c>
-      <c r="H18" s="62" t="n">
+      <c r="H18" s="61" t="n">
         <f aca="false">$D$6*H14</f>
         <v>609.57</v>
       </c>
-      <c r="I18" s="62" t="n">
+      <c r="I18" s="61" t="n">
         <f aca="false">$D$6*I14</f>
         <v>609.57</v>
       </c>
-      <c r="J18" s="62" t="n">
+      <c r="J18" s="61" t="n">
         <f aca="false">$D$6*J14</f>
         <v>609.57</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D19" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D19" s="61" t="n">
         <f aca="false">$D$7*D15</f>
         <v>450</v>
       </c>
-      <c r="E19" s="62" t="n">
+      <c r="E19" s="61" t="n">
         <f aca="false">$D$7*E15</f>
         <v>1950</v>
       </c>
-      <c r="F19" s="62" t="n">
+      <c r="F19" s="61" t="n">
         <f aca="false">$D$7*F15</f>
         <v>2550</v>
       </c>
-      <c r="G19" s="62" t="n">
+      <c r="G19" s="61" t="n">
         <f aca="false">$D$7*G15</f>
         <v>3000</v>
       </c>
-      <c r="H19" s="62" t="n">
+      <c r="H19" s="61" t="n">
         <f aca="false">$D$7*H15</f>
         <v>3000</v>
       </c>
-      <c r="I19" s="62" t="n">
+      <c r="I19" s="61" t="n">
         <f aca="false">$D$7*I15</f>
         <v>3000</v>
       </c>
-      <c r="J19" s="62" t="n">
+      <c r="J19" s="61" t="n">
         <f aca="false">$D$7*J15</f>
         <v>3000</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="C20" s="61"/>
-      <c r="D20" s="61"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
+        <v>236</v>
+      </c>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
+      <c r="J20" s="60"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D21" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D21" s="61" t="n">
         <v>247.88375</v>
       </c>
-      <c r="E21" s="62" t="n">
+      <c r="E21" s="61" t="n">
         <v>1284.86410416667</v>
       </c>
-      <c r="F21" s="62" t="n">
+      <c r="F21" s="61" t="n">
         <v>1669.08391666667</v>
       </c>
-      <c r="G21" s="62" t="n">
+      <c r="G21" s="61" t="n">
         <v>1970.6758125</v>
       </c>
-      <c r="H21" s="62" t="n">
+      <c r="H21" s="61" t="n">
         <v>1983.07</v>
       </c>
-      <c r="I21" s="62" t="n">
+      <c r="I21" s="61" t="n">
         <v>1983.07</v>
       </c>
-      <c r="J21" s="62" t="n">
+      <c r="J21" s="61" t="n">
         <v>1983.07</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D22" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D23" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D23" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D24" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D24" s="61" t="n">
         <v>76.19625</v>
       </c>
-      <c r="E24" s="62" t="n">
+      <c r="E24" s="61" t="n">
         <v>394.9505625</v>
       </c>
-      <c r="F24" s="62" t="n">
+      <c r="F24" s="61" t="n">
         <v>513.05475</v>
       </c>
-      <c r="G24" s="62" t="n">
+      <c r="G24" s="61" t="n">
         <v>605.7601875</v>
       </c>
-      <c r="H24" s="62" t="n">
+      <c r="H24" s="61" t="n">
         <v>609.57</v>
       </c>
-      <c r="I24" s="62" t="n">
+      <c r="I24" s="61" t="n">
         <v>609.57</v>
       </c>
-      <c r="J24" s="62" t="n">
+      <c r="J24" s="61" t="n">
         <v>609.57</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D25" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D25" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D26" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D26" s="61" t="n">
         <v>375</v>
       </c>
-      <c r="E26" s="62" t="n">
+      <c r="E26" s="61" t="n">
         <v>1943.75</v>
       </c>
-      <c r="F26" s="62" t="n">
+      <c r="F26" s="61" t="n">
         <v>2525</v>
       </c>
-      <c r="G26" s="62" t="n">
+      <c r="G26" s="61" t="n">
         <v>2981.25</v>
       </c>
-      <c r="H26" s="62" t="n">
+      <c r="H26" s="61" t="n">
         <v>3000</v>
       </c>
-      <c r="I26" s="62" t="n">
+      <c r="I26" s="61" t="n">
         <v>3000</v>
       </c>
-      <c r="J26" s="62" t="n">
+      <c r="J26" s="61" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="C27" s="61"/>
-      <c r="D27" s="61"/>
-      <c r="E27" s="61"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="61"/>
-      <c r="J27" s="61"/>
+        <v>243</v>
+      </c>
+      <c r="C27" s="60"/>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+      <c r="J27" s="60"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D28" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D28" s="61" t="n">
         <f aca="false">0+D17-D21-D22</f>
         <v>49.57675</v>
       </c>
-      <c r="E28" s="62" t="n">
+      <c r="E28" s="61" t="n">
         <f aca="false">D28+E17-E21-E22</f>
         <v>53.70814583333</v>
       </c>
-      <c r="F28" s="62" t="n">
+      <c r="F28" s="61" t="n">
         <f aca="false">E28+F17-F21-F22</f>
         <v>70.2337291666599</v>
       </c>
-      <c r="G28" s="62" t="n">
+      <c r="G28" s="61" t="n">
         <f aca="false">F28+G17-G21-G22</f>
         <v>82.6279166666598</v>
       </c>
-      <c r="H28" s="62" t="n">
+      <c r="H28" s="61" t="n">
         <f aca="false">G28+H17-H21-H22</f>
         <v>82.6279166666598</v>
       </c>
-      <c r="I28" s="62" t="n">
+      <c r="I28" s="61" t="n">
         <f aca="false">H28+I17-I21-I22</f>
         <v>82.6279166666598</v>
       </c>
-      <c r="J28" s="62" t="n">
+      <c r="J28" s="61" t="n">
         <f aca="false">I28+J17-J21-J22</f>
         <v>82.6279166666598</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D29" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D29" s="61" t="n">
         <f aca="false">0+D18-D23-D24</f>
         <v>15.23925</v>
       </c>
-      <c r="E29" s="62" t="n">
+      <c r="E29" s="61" t="n">
         <f aca="false">D29+E18-E23-E24</f>
         <v>16.5091875000001</v>
       </c>
-      <c r="F29" s="62" t="n">
+      <c r="F29" s="61" t="n">
         <f aca="false">E29+F18-F23-F24</f>
         <v>21.5889375000002</v>
       </c>
-      <c r="G29" s="62" t="n">
+      <c r="G29" s="61" t="n">
         <f aca="false">F29+G18-G23-G24</f>
         <v>25.3987500000002</v>
       </c>
-      <c r="H29" s="62" t="n">
+      <c r="H29" s="61" t="n">
         <f aca="false">G29+H18-H23-H24</f>
         <v>25.3987500000002</v>
       </c>
-      <c r="I29" s="62" t="n">
+      <c r="I29" s="61" t="n">
         <f aca="false">H29+I18-I23-I24</f>
         <v>25.3987500000002</v>
       </c>
-      <c r="J29" s="62" t="n">
+      <c r="J29" s="61" t="n">
         <f aca="false">I29+J18-J23-J24</f>
         <v>25.3987500000002</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="D30" s="62" t="n">
+        <v>228</v>
+      </c>
+      <c r="D30" s="61" t="n">
         <f aca="false">0+D19-D25-D26</f>
         <v>75</v>
       </c>
-      <c r="E30" s="62" t="n">
+      <c r="E30" s="61" t="n">
         <f aca="false">D30+E19-E25-E26</f>
         <v>81.25</v>
       </c>
-      <c r="F30" s="62" t="n">
+      <c r="F30" s="61" t="n">
         <f aca="false">E30+F19-F25-F26</f>
         <v>106.25</v>
       </c>
-      <c r="G30" s="62" t="n">
+      <c r="G30" s="61" t="n">
         <f aca="false">F30+G19-G25-G26</f>
         <v>125</v>
       </c>
-      <c r="H30" s="62" t="n">
+      <c r="H30" s="61" t="n">
         <f aca="false">G30+H19-H25-H26</f>
         <v>125</v>
       </c>
-      <c r="I30" s="62" t="n">
+      <c r="I30" s="61" t="n">
         <f aca="false">H30+I19-I25-I26</f>
         <v>125</v>
       </c>
-      <c r="J30" s="62" t="n">
+      <c r="J30" s="61" t="n">
         <f aca="false">I30+J19-J25-J26</f>
         <v>125</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
-      <c r="J31" s="61"/>
+        <v>244</v>
+      </c>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D32" s="30" t="n">
         <v>36542.2638937014</v>
@@ -16088,10 +16036,10 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D33" s="30" t="n">
         <v>0</v>
@@ -16117,10 +16065,10 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D34" s="30" t="n">
         <v>0</v>
@@ -16146,7 +16094,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -16187,10 +16135,10 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K2" s="52" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16235,20 +16183,20 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
+        <v>249</v>
+      </c>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
+      <c r="F6" s="60"/>
+      <c r="G6" s="60"/>
+      <c r="H6" s="60"/>
+      <c r="I6" s="60"/>
+      <c r="J6" s="60"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C7" s="20" t="s">
         <v>34</v>
@@ -16284,7 +16232,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C8" s="20" t="s">
         <v>34</v>
@@ -16320,7 +16268,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>34</v>
@@ -16392,20 +16340,20 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
+        <v>253</v>
+      </c>
+      <c r="C12" s="60"/>
+      <c r="D12" s="60"/>
+      <c r="E12" s="60"/>
+      <c r="F12" s="60"/>
+      <c r="G12" s="60"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="60"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C13" s="20" t="s">
         <v>34</v>
@@ -16441,7 +16389,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>34</v>
@@ -16477,7 +16425,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C15" s="20" t="s">
         <v>34</v>
@@ -16549,9 +16497,9 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="39" t="s">
-        <v>256</v>
-      </c>
-      <c r="C18" s="63" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="62" t="s">
         <v>34</v>
       </c>
       <c r="D18" s="17" t="n">
@@ -16585,10 +16533,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D19" s="15" t="n">
         <f aca="false">IFERROR(D10/D18,0)</f>
@@ -16660,43 +16608,43 @@
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G2" s="52" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="53" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="19" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>45</v>
       </c>
       <c r="D5" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="F5" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="G5" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="H5" s="19" t="s">
         <v>264</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="11" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
@@ -16707,16 +16655,16 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C7" s="20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D7" s="30" t="n">
         <f aca="false">IFERROR(F7/E7,0)</f>
         <v>11086.3935301997</v>
       </c>
-      <c r="E7" s="62" t="n">
+      <c r="E7" s="61" t="n">
         <v>50</v>
       </c>
       <c r="F7" s="14" t="n">
@@ -16726,22 +16674,22 @@
         <f aca="false">IFERROR(F7/$F$20,0)</f>
         <v>0.0202777420109502</v>
       </c>
-      <c r="H7" s="64" t="s">
-        <v>269</v>
+      <c r="H7" s="63" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D8" s="30" t="n">
         <f aca="false">IFERROR(F8/E8,0)</f>
         <v>12.3830808954653</v>
       </c>
-      <c r="E8" s="62" t="n">
+      <c r="E8" s="61" t="n">
         <v>2000</v>
       </c>
       <c r="F8" s="14" t="n">
@@ -16751,13 +16699,13 @@
         <f aca="false">IFERROR(F8/$F$20,0)</f>
         <v>0.000905978735158418</v>
       </c>
-      <c r="H8" s="64" t="s">
-        <v>269</v>
+      <c r="H8" s="63" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="26" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
@@ -16774,7 +16722,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="11" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C11" s="11"/>
       <c r="D11" s="11"/>
@@ -16785,16 +16733,16 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D12" s="30" t="n">
         <f aca="false">IFERROR(F12/E12,0)</f>
         <v>4937.03807066388</v>
       </c>
-      <c r="E12" s="62" t="n">
+      <c r="E12" s="61" t="n">
         <v>5000</v>
       </c>
       <c r="F12" s="14" t="n">
@@ -16804,22 +16752,22 @@
         <f aca="false">IFERROR(F12/$F$20,0)</f>
         <v>0.903016693593393</v>
       </c>
-      <c r="H12" s="64" t="s">
-        <v>275</v>
+      <c r="H12" s="63" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D13" s="30" t="n">
         <f aca="false">IFERROR(F13/E13,0)</f>
         <v>341.777802852018</v>
       </c>
-      <c r="E13" s="62" t="n">
+      <c r="E13" s="61" t="n">
         <v>1119.94</v>
       </c>
       <c r="F13" s="14" t="n">
@@ -16829,22 +16777,22 @@
         <f aca="false">IFERROR(F13/$F$20,0)</f>
         <v>0.0140022526073769</v>
       </c>
-      <c r="H13" s="64" t="s">
-        <v>269</v>
+      <c r="H13" s="63" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D14" s="30" t="n">
         <f aca="false">IFERROR(F14/E14,0)</f>
         <v>348.434711714666</v>
       </c>
-      <c r="E14" s="62" t="n">
+      <c r="E14" s="61" t="n">
         <v>3334.62</v>
       </c>
       <c r="F14" s="14" t="n">
@@ -16854,22 +16802,22 @@
         <f aca="false">IFERROR(F14/$F$20,0)</f>
         <v>0.0425037318262477</v>
       </c>
-      <c r="H14" s="64" t="s">
-        <v>269</v>
+      <c r="H14" s="63" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D15" s="30" t="n">
         <f aca="false">IFERROR(F15/E15,0)</f>
         <v>1080.5373280042</v>
       </c>
-      <c r="E15" s="62" t="n">
+      <c r="E15" s="61" t="n">
         <v>162.56</v>
       </c>
       <c r="F15" s="14" t="n">
@@ -16879,22 +16827,22 @@
         <f aca="false">IFERROR(F15/$F$20,0)</f>
         <v>0.00642558634046165</v>
       </c>
-      <c r="H15" s="64" t="s">
-        <v>269</v>
+      <c r="H15" s="63" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D16" s="30" t="n">
         <f aca="false">IFERROR(F16/E16,0)</f>
         <v>88.3084134538345</v>
       </c>
-      <c r="E16" s="62" t="n">
+      <c r="E16" s="61" t="n">
         <v>2000</v>
       </c>
       <c r="F16" s="14" t="n">
@@ -16904,22 +16852,22 @@
         <f aca="false">IFERROR(F16/$F$20,0)</f>
         <v>0.00646087556078634</v>
       </c>
-      <c r="H16" s="64" t="s">
-        <v>269</v>
+      <c r="H16" s="63" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D17" s="30" t="n">
         <f aca="false">IFERROR(F17/E17,0)</f>
         <v>872.945941900185</v>
       </c>
-      <c r="E17" s="62" t="n">
+      <c r="E17" s="61" t="n">
         <v>200.64</v>
       </c>
       <c r="F17" s="14" t="n">
@@ -16929,13 +16877,13 @@
         <f aca="false">IFERROR(F17/$F$20,0)</f>
         <v>0.00640713932562554</v>
       </c>
-      <c r="H17" s="64" t="s">
-        <v>269</v>
+      <c r="H17" s="63" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="26" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
@@ -16952,11 +16900,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="C20" s="65"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="65"/>
+        <v>280</v>
+      </c>
+      <c r="C20" s="64"/>
+      <c r="D20" s="64"/>
+      <c r="E20" s="64"/>
       <c r="F20" s="17" t="n">
         <f aca="false">F9+F18</f>
         <v>27336361.0312553</v>
@@ -16965,11 +16913,11 @@
         <f aca="false">IFERROR(F20/$F$20,0)</f>
         <v>1</v>
       </c>
-      <c r="H20" s="65"/>
+      <c r="H20" s="64"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="11"/>
@@ -16980,22 +16928,22 @@
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="19" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G23" s="19"/>
       <c r="H23" s="19" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
@@ -17004,13 +16952,13 @@
         <v>1018194.0197046</v>
       </c>
       <c r="G24" s="13"/>
-      <c r="H24" s="66" t="s">
-        <v>287</v>
+      <c r="H24" s="65" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="13" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
@@ -17019,13 +16967,13 @@
         <v>94026.7687233843</v>
       </c>
       <c r="G25" s="13"/>
-      <c r="H25" s="66" t="s">
-        <v>289</v>
+      <c r="H25" s="65" t="s">
+        <v>287</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -17039,7 +16987,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="26" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
